--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_SLIP-CSTD-0-01-B-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_SLIP-CSTD-0-01-B-C0.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\172.16.211.98\メータ改革_kk\99_temp\ois\050D\10_CV\10_設計\作成中\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\BEV\BEV設計・実装\課題管理一覧\フレーム変更漏れ対応\Alertパラメータ設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF596B7E-BDDA-471B-A393-DE09E26800B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="25974" yWindow="-109" windowWidth="26301" windowHeight="14305" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -21,17 +22,30 @@
     <sheet name="Reference" sheetId="3" r:id="rId7"/>
     <sheet name="History" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>YOSHIKI IWATA</author>
   </authors>
   <commentList>
-    <comment ref="B10" authorId="0" shapeId="0">
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -48,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -65,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0">
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -85,12 +99,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>鈴木　大助</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -136,7 +150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0" shapeId="0">
+    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -152,7 +166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -170,7 +184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P33" authorId="0" shapeId="0">
+    <comment ref="P33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -186,7 +200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q33" authorId="0" shapeId="0">
+    <comment ref="Q33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -207,13 +221,13 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>鈴木　大助</author>
     <author>YOSHIKI IWATA</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -228,7 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="1" shapeId="0">
+    <comment ref="F2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
       <text>
         <r>
           <rPr>
@@ -256,7 +270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="0" shapeId="0">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
       <text>
         <r>
           <rPr>
@@ -271,7 +285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="0" shapeId="0">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
       <text>
         <r>
           <rPr>
@@ -292,7 +306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
       <text>
         <r>
           <rPr>
@@ -307,7 +321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="1" shapeId="0">
+    <comment ref="J2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
       <text>
         <r>
           <rPr>
@@ -323,7 +337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K2" authorId="0" shapeId="0">
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
       <text>
         <r>
           <rPr>
@@ -339,7 +353,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L2" authorId="1" shapeId="0">
+    <comment ref="L2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
       <text>
         <r>
           <rPr>
@@ -354,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M2" authorId="1" shapeId="0">
+    <comment ref="M2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
       <text>
         <r>
           <rPr>
@@ -374,13 +388,13 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>YOSHIKI IWATA</author>
     <author>鈴木　大助</author>
   </authors>
   <commentList>
-    <comment ref="B6" authorId="0" shapeId="0">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
       <text>
         <r>
           <rPr>
@@ -397,7 +411,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C9" authorId="1" shapeId="0">
+    <comment ref="C9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
       <text>
         <r>
           <rPr>
@@ -413,7 +427,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="1" shapeId="0">
+    <comment ref="E9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000003000000}">
       <text>
         <r>
           <rPr>
@@ -429,7 +443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F9" authorId="1" shapeId="0">
+    <comment ref="F9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
       <text>
         <r>
           <rPr>
@@ -444,7 +458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G9" authorId="1" shapeId="0">
+    <comment ref="G9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
       <text>
         <r>
           <rPr>
@@ -460,7 +474,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H9" authorId="1" shapeId="0">
+    <comment ref="H9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000006000000}">
       <text>
         <r>
           <rPr>
@@ -476,7 +490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="1" shapeId="0">
+    <comment ref="I9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000007000000}">
       <text>
         <r>
           <rPr>
@@ -492,7 +506,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="1" shapeId="0">
+    <comment ref="J9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000008000000}">
       <text>
         <r>
           <rPr>
@@ -512,7 +526,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="321">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2458,10 +2472,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>VSC1S95_STS</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>－</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2527,14 +2537,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>VSC1S95</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VSC1S95</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>RWT_EN</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2560,10 +2562,6 @@
   </si>
   <si>
     <t>BAT_AO</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VSC1S95_STS</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3053,11 +3051,19 @@
     <t>DDRTWV_SIG</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>DDM1S17_STS</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DDM1S17</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="20">
     <font>
       <sz val="11"/>
@@ -5147,6 +5153,12 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5180,37 +5192,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5255,10 +5246,31 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5315,29 +5327,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="42">
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5386,13 +5385,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -5415,174 +5407,6 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5610,16 +5434,6 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -5675,7 +5489,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6452,6 +6272,60 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>47978</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="図 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="16590818" y="8520545"/>
+          <a:ext cx="18703637" cy="8533888"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>1</xdr:colOff>
       <xdr:row>117</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -6464,13 +6338,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="図 41"/>
+        <xdr:cNvPr id="42" name="図 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -6501,54 +6381,6 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>47978</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="図 34"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="16590818" y="8520545"/>
-          <a:ext cx="18703637" cy="8533888"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>173180</xdr:rowOff>
     </xdr:from>
@@ -6560,7 +6392,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="図 30"/>
+        <xdr:cNvPr id="31" name="図 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -6608,7 +6446,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8"/>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -6646,7 +6490,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="線吹き出し 1 (枠付き) 14"/>
+        <xdr:cNvPr id="15" name="線吹き出し 1 (枠付き) 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6729,7 +6579,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="線吹き出し 1 (枠付き) 19"/>
+        <xdr:cNvPr id="20" name="線吹き出し 1 (枠付き) 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6826,7 +6682,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="線吹き出し 1 (枠付き) 22"/>
+        <xdr:cNvPr id="23" name="線吹き出し 1 (枠付き) 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6945,7 +6807,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="正方形/長方形 26"/>
+        <xdr:cNvPr id="27" name="正方形/長方形 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7005,7 +6873,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="正方形/長方形 27"/>
+        <xdr:cNvPr id="28" name="正方形/長方形 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7065,7 +6939,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="正方形/長方形 28"/>
+        <xdr:cNvPr id="29" name="正方形/長方形 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7125,7 +7005,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="正方形/長方形 29"/>
+        <xdr:cNvPr id="30" name="正方形/長方形 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7185,7 +7071,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="線吹き出し 1 (枠付き) 31"/>
+        <xdr:cNvPr id="32" name="線吹き出し 1 (枠付き) 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7271,7 +7163,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="正方形/長方形 32"/>
+        <xdr:cNvPr id="33" name="正方形/長方形 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7331,7 +7229,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="線吹き出し 1 (枠付き) 33"/>
+        <xdr:cNvPr id="34" name="線吹き出し 1 (枠付き) 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7561,7 +7465,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="正方形/長方形 35"/>
+        <xdr:cNvPr id="36" name="正方形/長方形 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7621,7 +7531,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="線吹き出し 1 (枠付き) 36"/>
+        <xdr:cNvPr id="37" name="線吹き出し 1 (枠付き) 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7729,7 +7645,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="線吹き出し 1 (枠付き) 37"/>
+        <xdr:cNvPr id="38" name="線吹き出し 1 (枠付き) 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7815,7 +7737,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="線吹き出し 1 (枠付き) 38"/>
+        <xdr:cNvPr id="39" name="線吹き出し 1 (枠付き) 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7901,7 +7829,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="正方形/長方形 39"/>
+        <xdr:cNvPr id="40" name="正方形/長方形 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7961,7 +7895,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="正方形/長方形 40"/>
+        <xdr:cNvPr id="41" name="正方形/長方形 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8021,7 +7961,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="線吹き出し 1 (枠付き) 43"/>
+        <xdr:cNvPr id="44" name="線吹き出し 1 (枠付き) 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8148,7 +8094,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="線吹き出し 1 (枠付き) 44"/>
+        <xdr:cNvPr id="45" name="線吹き出し 1 (枠付き) 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8231,7 +8183,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="線吹き出し 1 (枠付き) 45"/>
+        <xdr:cNvPr id="46" name="線吹き出し 1 (枠付き) 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8308,17 +8266,6 @@
             </a:rPr>
             <a:t>として振舞う</a:t>
           </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t/>
-          </a:r>
           <a:br>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
               <a:solidFill>
@@ -8390,7 +8337,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="正方形/長方形 46"/>
+        <xdr:cNvPr id="47" name="正方形/長方形 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8450,7 +8403,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="線吹き出し 1 (枠付き) 47"/>
+        <xdr:cNvPr id="48" name="線吹き出し 1 (枠付き) 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8693,7 +8652,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="正方形/長方形 42"/>
+        <xdr:cNvPr id="43" name="正方形/長方形 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8753,7 +8718,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="線吹き出し 1 (枠付き) 48"/>
+        <xdr:cNvPr id="49" name="線吹き出し 1 (枠付き) 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8935,7 +8906,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="正方形/長方形 49"/>
+        <xdr:cNvPr id="50" name="正方形/長方形 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9029,7 +9006,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="図 50"/>
+        <xdr:cNvPr id="51" name="図 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -9077,7 +9060,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="図 51"/>
+        <xdr:cNvPr id="52" name="図 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -9125,7 +9114,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="図 52"/>
+        <xdr:cNvPr id="53" name="図 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -9173,7 +9168,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="線吹き出し 1 (枠付き) 53"/>
+        <xdr:cNvPr id="54" name="線吹き出し 1 (枠付き) 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9311,7 +9312,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="正方形/長方形 54"/>
+        <xdr:cNvPr id="55" name="正方形/長方形 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9356,13 +9363,289 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>295764</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123233</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>246469</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>24647</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE132759-A1D9-4DBD-AA85-A8CDD0A0D9BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20198135" y="14418436"/>
+          <a:ext cx="1183051" cy="1503461"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>529909</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123234</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>540057</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>8698</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="線吹き出し 1 (枠付き) 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3233AEFC-7EED-4019-B929-C60A98AD1C67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12643860" y="14098027"/>
+          <a:ext cx="2253017" cy="1167102"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 52087"/>
+            <a:gd name="adj2" fmla="val 100142"/>
+            <a:gd name="adj3" fmla="val 82032"/>
+            <a:gd name="adj4" fmla="val 338136"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>仕様の表記が誤っているが</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>BA</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>表より以下となる。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>〇「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>DDM1S17</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>✖「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>VSC1S95</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -9400,9 +9683,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -9437,7 +9720,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -9472,7 +9755,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9645,10 +9928,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:R13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="10" hidden="1" customWidth="1"/>
@@ -9665,18 +9948,18 @@
       <c r="H2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="251" t="s">
+      <c r="I2" s="253" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="251"/>
-      <c r="K2" s="251"/>
-      <c r="L2" s="251"/>
-      <c r="M2" s="251"/>
-      <c r="N2" s="251"/>
-      <c r="O2" s="251"/>
-      <c r="P2" s="251"/>
-      <c r="Q2" s="251"/>
-      <c r="R2" s="251"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="M2" s="253"/>
+      <c r="N2" s="253"/>
+      <c r="O2" s="253"/>
+      <c r="P2" s="253"/>
+      <c r="Q2" s="253"/>
+      <c r="R2" s="253"/>
     </row>
     <row r="3" spans="2:18" ht="25.5" customHeight="1">
       <c r="C3" s="7"/>
@@ -9689,18 +9972,18 @@
       <c r="H3" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="252" t="s">
+      <c r="I3" s="254" t="s">
         <v>204</v>
       </c>
-      <c r="J3" s="253"/>
-      <c r="K3" s="253"/>
-      <c r="L3" s="253"/>
-      <c r="M3" s="253"/>
-      <c r="N3" s="253"/>
-      <c r="O3" s="253"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
+      <c r="J3" s="255"/>
+      <c r="K3" s="255"/>
+      <c r="L3" s="255"/>
+      <c r="M3" s="255"/>
+      <c r="N3" s="255"/>
+      <c r="O3" s="255"/>
+      <c r="P3" s="255"/>
+      <c r="Q3" s="255"/>
+      <c r="R3" s="255"/>
     </row>
     <row r="4" spans="2:18" ht="25.5" customHeight="1">
       <c r="C4" s="7"/>
@@ -9724,34 +10007,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="14.25" thickBot="1"/>
+    <row r="6" spans="2:18" ht="13.6" thickBot="1"/>
     <row r="7" spans="2:18">
-      <c r="C7" s="245" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="246"/>
-      <c r="E7" s="247" t="s">
+      <c r="C7" s="247" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="248"/>
+      <c r="E7" s="249" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="247"/>
-      <c r="G7" s="248" t="s">
+      <c r="F7" s="249"/>
+      <c r="G7" s="250" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="248"/>
-      <c r="I7" s="248"/>
-      <c r="J7" s="248"/>
-      <c r="K7" s="248"/>
-      <c r="L7" s="248"/>
-      <c r="M7" s="249" t="s">
+      <c r="H7" s="250"/>
+      <c r="I7" s="250"/>
+      <c r="J7" s="250"/>
+      <c r="K7" s="250"/>
+      <c r="L7" s="250"/>
+      <c r="M7" s="251" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="249"/>
-      <c r="O7" s="249"/>
-      <c r="P7" s="249"/>
-      <c r="Q7" s="249"/>
-      <c r="R7" s="250"/>
-    </row>
-    <row r="8" spans="2:18" ht="27.75" thickBot="1">
+      <c r="N7" s="251"/>
+      <c r="O7" s="251"/>
+      <c r="P7" s="251"/>
+      <c r="Q7" s="251"/>
+      <c r="R7" s="252"/>
+    </row>
+    <row r="8" spans="2:18" ht="26.5" thickBot="1">
       <c r="B8" s="10" t="s">
         <v>90</v>
       </c>
@@ -9804,7 +10087,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="95.25" thickTop="1">
+    <row r="9" spans="2:18" ht="91.05" thickTop="1">
       <c r="B9" s="10">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -9812,8 +10095,8 @@
       <c r="C9" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="303" t="s">
-        <v>317</v>
+      <c r="D9" s="245" t="s">
+        <v>313</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>31</v>
@@ -9844,7 +10127,7 @@
       <c r="O9" s="14"/>
       <c r="P9" s="241"/>
       <c r="Q9" s="14" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="R9" s="193">
         <v>44375</v>
@@ -9916,7 +10199,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="2:18" ht="14.25" thickBot="1">
+    <row r="13" spans="2:18" ht="13.6" thickBot="1">
       <c r="B13" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9949,18 +10232,21 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1"/>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="4.625" customWidth="1"/>
     <col min="3" max="3" width="3.5" customWidth="1"/>
@@ -9978,13 +10264,13 @@
         <v>143</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.25" thickBot="1">
+    <row r="6" spans="2:5" ht="13.6" thickBot="1">
       <c r="B6" s="156" t="s">
         <v>134</v>
       </c>
       <c r="C6" s="156"/>
     </row>
-    <row r="7" spans="2:5" ht="14.25" thickBot="1">
+    <row r="7" spans="2:5" ht="13.6" thickBot="1">
       <c r="C7" s="79" t="s">
         <v>136</v>
       </c>
@@ -10004,7 +10290,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="27">
+    <row r="9" spans="2:5" ht="25.85">
       <c r="C9" s="166">
         <v>1</v>
       </c>
@@ -10015,7 +10301,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="14.25" thickBot="1">
+    <row r="10" spans="2:5" ht="13.6" thickBot="1">
       <c r="C10" s="164"/>
       <c r="D10" s="90"/>
       <c r="E10" s="6"/>
@@ -10023,14 +10309,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="162"/>
     </row>
-    <row r="12" spans="2:5" ht="14.25" thickBot="1">
+    <row r="12" spans="2:5" ht="13.6" thickBot="1">
       <c r="B12" s="157" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="86"/>
       <c r="D12" s="86"/>
     </row>
-    <row r="13" spans="2:5" ht="14.25" thickBot="1">
+    <row r="13" spans="2:5" ht="13.6" thickBot="1">
       <c r="B13" s="158"/>
       <c r="C13" s="163" t="s">
         <v>136</v>
@@ -10042,7 +10328,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="14.25" thickTop="1">
+    <row r="14" spans="2:5" ht="13.6" thickTop="1">
       <c r="C14" s="160">
         <v>0</v>
       </c>
@@ -10119,17 +10405,17 @@
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="14.25" thickBot="1">
+    <row r="21" spans="2:5" ht="13.6" thickBot="1">
       <c r="C21" s="164"/>
       <c r="D21" s="90"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="24" spans="2:5" ht="14.25" thickBot="1">
+    <row r="24" spans="2:5" ht="13.6" thickBot="1">
       <c r="B24" s="156" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="14.25" thickBot="1">
+    <row r="25" spans="2:5" ht="13.6" thickBot="1">
       <c r="C25" s="163" t="s">
         <v>136</v>
       </c>
@@ -10151,7 +10437,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="120" customHeight="1">
+    <row r="27" spans="2:5" ht="120.1" customHeight="1">
       <c r="C27" s="161">
         <v>1</v>
       </c>
@@ -10216,26 +10502,26 @@
       <c r="D33" s="89"/>
       <c r="E33" s="75"/>
     </row>
-    <row r="34" spans="2:5" ht="14.25" thickBot="1">
+    <row r="34" spans="2:5" ht="13.6" thickBot="1">
       <c r="C34" s="164"/>
       <c r="D34" s="90"/>
       <c r="E34" s="6"/>
     </row>
-    <row r="37" spans="2:5" ht="14.25" thickBot="1">
+    <row r="37" spans="2:5" ht="13.6" thickBot="1">
       <c r="B37" s="156" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="254"/>
-      <c r="D38" s="255"/>
+      <c r="C38" s="256"/>
+      <c r="D38" s="257"/>
       <c r="E38" s="115" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="14.25" thickBot="1">
-      <c r="C39" s="256"/>
-      <c r="D39" s="257"/>
+    <row r="39" spans="2:5" ht="13.6" thickBot="1">
+      <c r="C39" s="258"/>
+      <c r="D39" s="259"/>
       <c r="E39" s="6" t="s">
         <v>122</v>
       </c>
@@ -10247,21 +10533,24 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="E8" r:id="rId1"/>
-    <hyperlink ref="E9" r:id="rId2"/>
+    <hyperlink ref="E8" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="E9" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
@@ -10271,121 +10560,121 @@
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.6" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="283" t="s">
+      <c r="B2" s="260" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="284"/>
-      <c r="D2" s="271" t="s">
-        <v>314</v>
-      </c>
-      <c r="E2" s="272"/>
-      <c r="F2" s="272"/>
-      <c r="G2" s="272"/>
-      <c r="H2" s="273"/>
+      <c r="C2" s="261"/>
+      <c r="D2" s="266" t="s">
+        <v>310</v>
+      </c>
+      <c r="E2" s="267"/>
+      <c r="F2" s="267"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="268"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="258" t="s">
+      <c r="B3" s="262" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="259"/>
-      <c r="D3" s="274" t="s">
-        <v>315</v>
-      </c>
-      <c r="E3" s="275"/>
-      <c r="F3" s="275"/>
-      <c r="G3" s="275"/>
-      <c r="H3" s="276"/>
-    </row>
-    <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="269" t="s">
+      <c r="C3" s="263"/>
+      <c r="D3" s="269" t="s">
+        <v>311</v>
+      </c>
+      <c r="E3" s="270"/>
+      <c r="F3" s="270"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="271"/>
+    </row>
+    <row r="4" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B4" s="264" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="270"/>
-      <c r="D4" s="277" t="str">
+      <c r="C4" s="265"/>
+      <c r="D4" s="272" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_C_SLIP-CSTD-0-01-B-C0.c</v>
       </c>
-      <c r="E4" s="278"/>
-      <c r="F4" s="278"/>
-      <c r="G4" s="278"/>
-      <c r="H4" s="279"/>
-    </row>
-    <row r="5" spans="2:14" ht="14.25" thickBot="1">
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
+      <c r="H4" s="274"/>
+    </row>
+    <row r="5" spans="2:14" ht="13.6" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="283" t="s">
+      <c r="B6" s="260" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="284"/>
-      <c r="D6" s="280" t="str">
+      <c r="C6" s="261"/>
+      <c r="D6" s="275" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>C_SLIP</v>
       </c>
-      <c r="E6" s="281"/>
-      <c r="F6" s="281"/>
-      <c r="G6" s="281"/>
-      <c r="H6" s="282"/>
+      <c r="E6" s="276"/>
+      <c r="F6" s="276"/>
+      <c r="G6" s="276"/>
+      <c r="H6" s="277"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="258" t="s">
+      <c r="B7" s="262" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="259"/>
-      <c r="D7" s="260">
+      <c r="C7" s="263"/>
+      <c r="D7" s="278">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="261"/>
-      <c r="F7" s="261"/>
-      <c r="G7" s="261"/>
-      <c r="H7" s="262"/>
+      <c r="E7" s="279"/>
+      <c r="F7" s="279"/>
+      <c r="G7" s="279"/>
+      <c r="H7" s="280"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="258" t="s">
+      <c r="B8" s="262" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="259"/>
-      <c r="D8" s="260" t="str">
+      <c r="C8" s="263"/>
+      <c r="D8" s="278" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_C_SLIP_MTRX</v>
       </c>
-      <c r="E8" s="261"/>
-      <c r="F8" s="261"/>
-      <c r="G8" s="261"/>
-      <c r="H8" s="262"/>
+      <c r="E8" s="279"/>
+      <c r="F8" s="279"/>
+      <c r="G8" s="279"/>
+      <c r="H8" s="280"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="258" t="s">
+      <c r="B9" s="262" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="259"/>
-      <c r="D9" s="263" t="s">
-        <v>313</v>
-      </c>
-      <c r="E9" s="264"/>
-      <c r="F9" s="264"/>
-      <c r="G9" s="264"/>
-      <c r="H9" s="265"/>
-    </row>
-    <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="269" t="s">
+      <c r="C9" s="263"/>
+      <c r="D9" s="281" t="s">
+        <v>309</v>
+      </c>
+      <c r="E9" s="282"/>
+      <c r="F9" s="282"/>
+      <c r="G9" s="282"/>
+      <c r="H9" s="283"/>
+    </row>
+    <row r="10" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B10" s="264" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="270"/>
-      <c r="D10" s="266"/>
-      <c r="E10" s="267"/>
-      <c r="F10" s="267"/>
-      <c r="G10" s="267"/>
-      <c r="H10" s="268"/>
-    </row>
-    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
-    <row r="12" spans="2:14" ht="14.25" thickBot="1">
+      <c r="C10" s="265"/>
+      <c r="D10" s="284"/>
+      <c r="E10" s="285"/>
+      <c r="F10" s="285"/>
+      <c r="G10" s="285"/>
+      <c r="H10" s="286"/>
+    </row>
+    <row r="11" spans="2:14" ht="13.6" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.6" thickBot="1">
       <c r="B12" s="147" t="s">
         <v>34</v>
       </c>
@@ -10420,18 +10709,18 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="14.25" thickTop="1">
+    <row r="13" spans="2:14" ht="13.6" thickTop="1">
       <c r="B13" s="108">
         <v>1</v>
       </c>
       <c r="C13" s="113" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D13" s="114" t="s">
         <v>48</v>
       </c>
       <c r="E13" s="114" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F13" s="53" t="str">
         <f t="shared" ref="F13:F37" ca="1" si="0">IF($D13&lt;&gt;"","u4_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"Srcchk","")</f>
@@ -11273,7 +11562,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="14.25" thickBot="1">
+    <row r="37" spans="2:14" ht="13.6" thickBot="1">
       <c r="B37" s="99">
         <v>25</v>
       </c>
@@ -11314,62 +11603,65 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
-    <cfRule type="expression" dxfId="41" priority="4">
+    <cfRule type="expression" dxfId="14" priority="4">
       <formula>14&lt;LEN($D$6)+LEN($C13)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="NG">
+      <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="40" priority="3">
+    <cfRule type="expression" dxfId="12" priority="3">
       <formula>14 &lt; LEN($D$6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5">
-    <cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E37" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"○,－"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D37" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>$K$13:$K$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>$L$13:$L$14</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
@@ -11383,7 +11675,7 @@
     <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="14.25" thickBot="1">
+    <row r="2" spans="2:18" ht="13.6" thickBot="1">
       <c r="B2" t="s">
         <v>194</v>
       </c>
@@ -11391,7 +11683,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="14.25" thickBot="1">
+    <row r="3" spans="2:18" ht="13.6" thickBot="1">
       <c r="B3" s="147" t="s">
         <v>34</v>
       </c>
@@ -11429,7 +11721,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B4" s="178">
         <v>0</v>
       </c>
@@ -11457,22 +11749,22 @@
       </c>
       <c r="R4" s="145"/>
     </row>
-    <row r="5" spans="2:18" ht="27.75" thickTop="1">
+    <row r="5" spans="2:18" ht="26.5" thickTop="1">
       <c r="B5" s="181">
         <v>1</v>
       </c>
       <c r="C5" s="210" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D5" s="110" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E5" s="69" t="str">
         <f ca="1">IF($C5&lt;&gt;"","ALERT_" &amp; D5 &amp; "_ID_"&amp;UPPER(Matrix!$D$6) &amp; "_" &amp; $C5,"")</f>
         <v>ALERT_OPT_ID_C_SLIP_VSCEXIST</v>
       </c>
       <c r="F5" s="240" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G5" s="69">
         <f ca="1">IF(E5&lt;&gt;"",LEN(E5),"")</f>
@@ -11991,7 +12283,7 @@
       <c r="Q28" s="151"/>
       <c r="R28" s="120"/>
     </row>
-    <row r="29" spans="2:18" ht="14.25" thickBot="1">
+    <row r="29" spans="2:18" ht="13.6" thickBot="1">
       <c r="B29" s="182">
         <v>25</v>
       </c>
@@ -12013,7 +12305,7 @@
       <c r="Q29" s="149"/>
       <c r="R29" s="122"/>
     </row>
-    <row r="32" spans="2:18" ht="14.25" thickBot="1">
+    <row r="32" spans="2:18" ht="13.6" thickBot="1">
       <c r="B32" t="s">
         <v>195</v>
       </c>
@@ -12021,7 +12313,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="14.25" thickBot="1">
+    <row r="33" spans="2:18" ht="13.6" thickBot="1">
       <c r="B33" s="147" t="s">
         <v>34</v>
       </c>
@@ -12053,7 +12345,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B34" s="178">
         <v>0</v>
       </c>
@@ -12079,7 +12371,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="14.25" thickTop="1">
+    <row r="35" spans="2:18" ht="13.6" thickTop="1">
       <c r="B35" s="181">
         <v>1</v>
       </c>
@@ -12607,7 +12899,7 @@
       <c r="Q58" s="151"/>
       <c r="R58" s="183"/>
     </row>
-    <row r="59" spans="2:18" ht="14.25" thickBot="1">
+    <row r="59" spans="2:18" ht="13.6" thickBot="1">
       <c r="B59" s="182">
         <v>25</v>
       </c>
@@ -12636,26 +12928,29 @@
   </protectedRanges>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D29">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D29" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"OPT,HW"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35:D59">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35:D59" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"DEF"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="28.375" customWidth="1"/>
     <col min="3" max="3" width="15.875" customWidth="1"/>
@@ -12670,12 +12965,12 @@
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.25" thickBot="1">
+    <row r="1" spans="2:21" ht="13.6" thickBot="1">
       <c r="C1" s="92" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="14.25" thickBot="1">
+    <row r="2" spans="2:21" ht="13.6" thickBot="1">
       <c r="B2" s="100" t="s">
         <v>58</v>
       </c>
@@ -12719,7 +13014,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14.3" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="25"/>
       <c r="C3" s="52" t="s">
         <v>107</v>
@@ -12740,12 +13035,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="14.25" thickTop="1">
+    <row r="4" spans="2:21" ht="13.6" thickTop="1">
       <c r="B4" s="25" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C4" s="109" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D4" s="116">
         <v>0</v>
@@ -12754,7 +13049,7 @@
         <v>129</v>
       </c>
       <c r="F4" s="208" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="G4" s="117" t="s">
         <v>129</v>
@@ -12792,10 +13087,10 @@
     </row>
     <row r="5" spans="2:21">
       <c r="B5" s="25" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C5" s="110" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D5" s="119">
         <v>1</v>
@@ -12804,7 +13099,7 @@
         <v>129</v>
       </c>
       <c r="F5" s="208" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G5" s="25" t="s">
         <v>129</v>
@@ -12842,19 +13137,19 @@
     </row>
     <row r="6" spans="2:21">
       <c r="B6" s="25" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D6" s="123">
         <v>2</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F6" s="209" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G6" s="111" t="s">
         <v>129</v>
@@ -12892,19 +13187,19 @@
     </row>
     <row r="7" spans="2:21">
       <c r="B7" s="227" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C7" s="217" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D7" s="228">
         <v>3</v>
       </c>
       <c r="E7" s="227" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F7" s="219" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G7" s="227" t="s">
         <v>129</v>
@@ -12919,10 +13214,10 @@
         <v>130</v>
       </c>
       <c r="K7" s="227" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="L7" s="219" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="M7" s="48">
         <f t="shared" ca="1" si="1"/>
@@ -13074,7 +13369,7 @@
       </c>
       <c r="U12" s="33"/>
     </row>
-    <row r="13" spans="2:21" ht="14.25" thickBot="1">
+    <row r="13" spans="2:21" ht="13.6" thickBot="1">
       <c r="B13" s="25"/>
       <c r="C13" s="24"/>
       <c r="D13" s="119"/>
@@ -15325,7 +15620,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="14.25" thickBot="1">
+    <row r="103" spans="2:15" ht="13.6" thickBot="1">
       <c r="B103" s="54"/>
       <c r="C103" s="55"/>
       <c r="D103" s="121"/>
@@ -15356,33 +15651,31 @@
     <protectedRange sqref="B4:L103" name="範囲1"/>
   </protectedRanges>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="M4:M103">
-    <cfRule type="cellIs" dxfId="38" priority="2" operator="greaterThan">
-      <formula>32</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="M3:M103">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="greaterThan">
       <formula>32</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 G3 I3 E3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 G3 I3 E3" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"あり,なし"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000001000000}">
           <x14:formula1>
             <xm:f>Matrix!$H$13:$H$37</xm:f>
           </x14:formula1>
           <xm:sqref>B3:B103</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000002000000}">
           <x14:formula1>
             <xm:f>Config_IF!$C$4:$C$29</xm:f>
           </x14:formula1>
@@ -15395,12 +15688,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
@@ -15427,7 +15720,7 @@
       <c r="B2" s="129" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="285" t="s">
+      <c r="C2" s="287" t="s">
         <v>81</v>
       </c>
       <c r="D2" s="59">
@@ -15526,16 +15819,16 @@
       <c r="AI2" s="59">
         <v>0</v>
       </c>
-      <c r="AJ2" s="287" t="s">
+      <c r="AJ2" s="289" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="213" customHeight="1" thickBot="1">
-      <c r="B3" s="304" t="str">
+    <row r="3" spans="1:49" ht="212.95" customHeight="1" thickBot="1">
+      <c r="B3" s="246" t="str">
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="286"/>
+      <c r="C3" s="288"/>
       <c r="D3" s="131" t="s">
         <v>61</v>
       </c>
@@ -15615,27 +15908,27 @@
         <v>66</v>
       </c>
       <c r="AD3" s="207" t="s">
-        <v>322</v>
-      </c>
-      <c r="AE3" s="293" t="s">
-        <v>205</v>
-      </c>
-      <c r="AF3" s="294"/>
-      <c r="AG3" s="293" t="s">
-        <v>321</v>
-      </c>
-      <c r="AH3" s="295"/>
-      <c r="AI3" s="294"/>
-      <c r="AJ3" s="288"/>
+        <v>318</v>
+      </c>
+      <c r="AE3" s="295" t="s">
+        <v>319</v>
+      </c>
+      <c r="AF3" s="296"/>
+      <c r="AG3" s="295" t="s">
+        <v>317</v>
+      </c>
+      <c r="AH3" s="297"/>
+      <c r="AI3" s="296"/>
+      <c r="AJ3" s="290"/>
       <c r="AR3" s="93" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A4" s="289" t="s">
+    <row r="4" spans="1:49" ht="13.6" thickBot="1">
+      <c r="A4" s="291" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="290"/>
+      <c r="B4" s="292"/>
       <c r="C4" s="141"/>
       <c r="D4" s="141"/>
       <c r="E4" s="141"/>
@@ -15679,9 +15972,9 @@
       <c r="AV4" s="82"/>
       <c r="AW4" s="83"/>
     </row>
-    <row r="5" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A5" s="291"/>
-      <c r="B5" s="292"/>
+    <row r="5" spans="1:49" ht="13.6" thickBot="1">
+      <c r="A5" s="293"/>
+      <c r="B5" s="294"/>
       <c r="C5" s="142"/>
       <c r="D5" s="142"/>
       <c r="E5" s="142"/>
@@ -15863,7 +16156,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_UNKNOWN,                                                     /* 00 UNKNOWN                                         */</v>
       </c>
       <c r="AU6" s="64" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AV6" s="49" t="s">
         <v>68</v>
@@ -15955,7 +16248,7 @@
         <v>67</v>
       </c>
       <c r="AC7" s="62" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AD7" s="230">
         <v>0</v>
@@ -16109,7 +16402,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="24" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="AL8" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16372,7 +16665,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="24" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AL10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16484,7 +16777,7 @@
         <v>67</v>
       </c>
       <c r="AC11" s="62" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AD11" s="230">
         <v>0</v>
@@ -16768,7 +17061,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" s="24" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AL13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17186,7 +17479,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_UNKNOWN,                                                     /* 10 UNKNOWN                                         */</v>
       </c>
       <c r="AU16" s="64" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AV16" s="50" t="s">
         <v>76</v>
@@ -17196,7 +17489,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="14.25" thickBot="1">
+    <row r="17" spans="2:49" ht="13.6" thickBot="1">
       <c r="B17" s="138"/>
       <c r="C17" s="48">
         <f t="shared" si="2"/>
@@ -17318,7 +17611,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_UNKNOWN,                                                     /* 11 UNKNOWN                                         */</v>
       </c>
       <c r="AU17" s="65" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AV17" s="51" t="s">
         <v>77</v>
@@ -17919,7 +18212,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" s="24" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL22" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18041,7 +18334,7 @@
         <v>1</v>
       </c>
       <c r="AJ23" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL23" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18163,7 +18456,7 @@
         <v>0</v>
       </c>
       <c r="AJ24" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL24" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18285,7 +18578,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18407,7 +18700,7 @@
         <v>0</v>
       </c>
       <c r="AJ26" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL26" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18529,7 +18822,7 @@
         <v>1</v>
       </c>
       <c r="AJ27" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL27" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18651,7 +18944,7 @@
         <v>0</v>
       </c>
       <c r="AJ28" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL28" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18773,7 +19066,7 @@
         <v>1</v>
       </c>
       <c r="AJ29" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL29" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18895,7 +19188,7 @@
         <v>0</v>
       </c>
       <c r="AJ30" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL30" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19017,7 +19310,7 @@
         <v>1</v>
       </c>
       <c r="AJ31" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL31" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19139,7 +19432,7 @@
         <v>0</v>
       </c>
       <c r="AJ32" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL32" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19261,7 +19554,7 @@
         <v>1</v>
       </c>
       <c r="AJ33" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL33" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19383,7 +19676,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL34" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19505,7 +19798,7 @@
         <v>1</v>
       </c>
       <c r="AJ35" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL35" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19627,7 +19920,7 @@
         <v>0</v>
       </c>
       <c r="AJ36" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL36" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19749,7 +20042,7 @@
         <v>1</v>
       </c>
       <c r="AJ37" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL37" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20115,7 +20408,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" s="24" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="AL40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20359,7 +20652,7 @@
         <v>0</v>
       </c>
       <c r="AJ42" s="24" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AL42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20725,7 +21018,7 @@
         <v>1</v>
       </c>
       <c r="AJ45" s="24" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL45" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21823,7 +22116,7 @@
         <v>0</v>
       </c>
       <c r="AJ54" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL54" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21945,7 +22238,7 @@
         <v>1</v>
       </c>
       <c r="AJ55" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL55" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22067,7 +22360,7 @@
         <v>0</v>
       </c>
       <c r="AJ56" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL56" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22189,7 +22482,7 @@
         <v>1</v>
       </c>
       <c r="AJ57" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL57" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22311,7 +22604,7 @@
         <v>0</v>
       </c>
       <c r="AJ58" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL58" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22433,7 +22726,7 @@
         <v>1</v>
       </c>
       <c r="AJ59" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL59" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22555,7 +22848,7 @@
         <v>0</v>
       </c>
       <c r="AJ60" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL60" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22677,7 +22970,7 @@
         <v>1</v>
       </c>
       <c r="AJ61" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL61" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22799,7 +23092,7 @@
         <v>0</v>
       </c>
       <c r="AJ62" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL62" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22921,7 +23214,7 @@
         <v>1</v>
       </c>
       <c r="AJ63" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL63" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23043,7 +23336,7 @@
         <v>0</v>
       </c>
       <c r="AJ64" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL64" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23165,7 +23458,7 @@
         <v>1</v>
       </c>
       <c r="AJ65" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL65" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23287,7 +23580,7 @@
         <v>0</v>
       </c>
       <c r="AJ66" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL66" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23409,7 +23702,7 @@
         <v>1</v>
       </c>
       <c r="AJ67" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL67" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23531,7 +23824,7 @@
         <v>0</v>
       </c>
       <c r="AJ68" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL68" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23653,7 +23946,7 @@
         <v>1</v>
       </c>
       <c r="AJ69" s="222" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL69" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -23672,7 +23965,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_C_SLIP_MALFUNC_RW                                            /* 63 MALFUNC_RW                                      */</v>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="14.25" thickBot="1">
+    <row r="70" spans="1:46" ht="13.6" thickBot="1">
       <c r="A70" s="57" t="s">
         <v>64</v>
       </c>
@@ -44265,161 +44558,60 @@
     <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="D6:AB11 D12:AC13 AG12:AI21 D14:AD21 D22:AC69">
-    <cfRule type="cellIs" dxfId="36" priority="46" operator="equal">
+  <conditionalFormatting sqref="D6:AB11 D12:AC13 D14:AD21">
+    <cfRule type="cellIs" dxfId="10" priority="47" operator="equal">
+      <formula>"×"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="46" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="47" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:AI69">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+      <formula>"×"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC6:AI6 AC7:AC11">
+    <cfRule type="cellIs" dxfId="6" priority="43" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="44" operator="equal">
+      <formula>"×"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD7:AD13">
+    <cfRule type="cellIs" dxfId="4" priority="39" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="40" operator="equal">
+      <formula>"×"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE7:AI21">
+    <cfRule type="cellIs" dxfId="2" priority="35" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="36" operator="equal">
       <formula>"×"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR5:AS70">
-    <cfRule type="expression" dxfId="34" priority="45">
+    <cfRule type="expression" dxfId="0" priority="45">
       <formula>$B$3="Index Table"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC6:AI6 AG10:AI11 AE7:AI9 AC7:AC11">
-    <cfRule type="cellIs" dxfId="33" priority="43" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="44" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE10:AF13">
-    <cfRule type="cellIs" dxfId="31" priority="41" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="42" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD7:AD13">
-    <cfRule type="cellIs" dxfId="29" priority="39" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="40" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE14:AF17">
-    <cfRule type="cellIs" dxfId="27" priority="37" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="38" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE18:AF21">
-    <cfRule type="cellIs" dxfId="25" priority="35" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="36" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG28:AI37 AD30:AD37">
-    <cfRule type="cellIs" dxfId="23" priority="33" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="34" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD22:AI22 AG23:AI27">
-    <cfRule type="cellIs" dxfId="21" priority="31" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="32" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD54:AI54 AG55:AI59">
-    <cfRule type="cellIs" dxfId="19" priority="7" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD23:AD29">
-    <cfRule type="cellIs" dxfId="17" priority="27" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="28" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE55:AF69">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE23:AF37">
-    <cfRule type="cellIs" dxfId="13" priority="21" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="22" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG44:AI53 AD46:AD53">
-    <cfRule type="cellIs" dxfId="11" priority="19" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="20" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD38:AI38 AG39:AI43">
-    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="18" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD39:AD45">
-    <cfRule type="cellIs" dxfId="7" priority="15" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="16" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE39:AF53">
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="12" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG60:AI69 AD62:AD69">
-    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="10" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD55:AD61">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000000000000}">
           <x14:formula1>
             <xm:f>CH_Design!$C$3:$C$103</xm:f>
           </x14:formula1>
@@ -44432,10 +44624,10 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:AS91"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="41" customWidth="1"/>
     <col min="3" max="10" width="3.375" customWidth="1"/>
@@ -44447,12 +44639,12 @@
     <col min="18" max="18" width="14.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:45" ht="15" thickBot="1">
+    <row r="2" spans="2:45" ht="15.65" thickBot="1">
       <c r="B2" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U2" s="206" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="V2" s="206"/>
       <c r="W2" s="206"/>
@@ -44479,20 +44671,20 @@
       <c r="AR2" s="206"/>
       <c r="AS2" s="206"/>
     </row>
-    <row r="3" spans="2:45" ht="15" thickBot="1">
+    <row r="3" spans="2:45" ht="15.65" thickBot="1">
       <c r="B3" s="97" t="s">
-        <v>209</v>
-      </c>
-      <c r="C3" s="300" t="s">
-        <v>299</v>
-      </c>
-      <c r="D3" s="301"/>
-      <c r="E3" s="301"/>
-      <c r="F3" s="301"/>
-      <c r="G3" s="301"/>
-      <c r="H3" s="301"/>
-      <c r="I3" s="301"/>
-      <c r="J3" s="302"/>
+        <v>208</v>
+      </c>
+      <c r="C3" s="302" t="s">
+        <v>295</v>
+      </c>
+      <c r="D3" s="303"/>
+      <c r="E3" s="303"/>
+      <c r="F3" s="303"/>
+      <c r="G3" s="303"/>
+      <c r="H3" s="303"/>
+      <c r="I3" s="303"/>
+      <c r="J3" s="304"/>
       <c r="K3" s="174"/>
       <c r="L3" s="174"/>
       <c r="M3" s="174"/>
@@ -44505,7 +44697,7 @@
     <row r="4" spans="2:45">
       <c r="B4" s="71"/>
       <c r="C4" s="36" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D4" s="36"/>
       <c r="E4" s="36"/>
@@ -44518,7 +44710,7 @@
       <c r="L4" s="36"/>
       <c r="M4" s="37"/>
       <c r="N4" s="32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O4" s="44" t="s">
         <v>21</v>
@@ -44531,16 +44723,16 @@
       <c r="B5" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="296" t="s">
-        <v>212</v>
-      </c>
-      <c r="D5" s="297"/>
-      <c r="E5" s="297"/>
-      <c r="F5" s="297"/>
-      <c r="G5" s="297"/>
-      <c r="H5" s="297"/>
-      <c r="I5" s="297"/>
-      <c r="J5" s="298"/>
+      <c r="C5" s="298" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="299"/>
+      <c r="E5" s="299"/>
+      <c r="F5" s="299"/>
+      <c r="G5" s="299"/>
+      <c r="H5" s="299"/>
+      <c r="I5" s="299"/>
+      <c r="J5" s="300"/>
       <c r="K5" s="197" t="s">
         <v>23</v>
       </c>
@@ -44551,7 +44743,7 @@
         <v>23</v>
       </c>
       <c r="N5" s="33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="O5" s="30" t="s">
         <v>24</v>
@@ -44566,183 +44758,183 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:45" ht="40.5">
+    <row r="6" spans="2:45" ht="38.75">
       <c r="B6" s="72" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="169" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" s="169" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" s="169" t="s">
         <v>214</v>
       </c>
-      <c r="D6" s="169" t="s">
+      <c r="F6" s="169" t="s">
+        <v>215</v>
+      </c>
+      <c r="G6" s="169" t="s">
         <v>214</v>
       </c>
-      <c r="E6" s="169" t="s">
+      <c r="H6" s="169" t="s">
         <v>215</v>
       </c>
-      <c r="F6" s="169" t="s">
+      <c r="I6" s="169" t="s">
+        <v>213</v>
+      </c>
+      <c r="J6" s="169" t="s">
+        <v>213</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="G6" s="169" t="s">
-        <v>215</v>
-      </c>
-      <c r="H6" s="169" t="s">
-        <v>216</v>
-      </c>
-      <c r="I6" s="169" t="s">
-        <v>214</v>
-      </c>
-      <c r="J6" s="169" t="s">
-        <v>214</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="144" t="s">
         <v>217</v>
-      </c>
-      <c r="L6" s="144" t="s">
-        <v>218</v>
       </c>
       <c r="M6" s="143" t="s">
         <v>200</v>
       </c>
       <c r="N6" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O6" s="41"/>
       <c r="P6" s="78"/>
       <c r="Q6" s="78"/>
       <c r="R6" s="91" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="7" spans="2:45" ht="27">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="2:45" ht="25.85">
       <c r="B7" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="299" t="s">
-        <v>220</v>
-      </c>
-      <c r="D7" s="297"/>
-      <c r="E7" s="297"/>
-      <c r="F7" s="297"/>
-      <c r="G7" s="297"/>
-      <c r="H7" s="297"/>
-      <c r="I7" s="297"/>
-      <c r="J7" s="298"/>
+      <c r="C7" s="301" t="s">
+        <v>219</v>
+      </c>
+      <c r="D7" s="299"/>
+      <c r="E7" s="299"/>
+      <c r="F7" s="299"/>
+      <c r="G7" s="299"/>
+      <c r="H7" s="299"/>
+      <c r="I7" s="299"/>
+      <c r="J7" s="300"/>
       <c r="K7" s="1" t="s">
-        <v>221</v>
+        <v>320</v>
       </c>
       <c r="L7" s="28" t="s">
-        <v>222</v>
+        <v>320</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>222</v>
+        <v>320</v>
       </c>
       <c r="N7" s="34"/>
       <c r="O7" s="41"/>
       <c r="P7" s="78"/>
       <c r="Q7" s="78"/>
       <c r="R7" s="75" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="8" spans="2:45" ht="136.5">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="8" spans="2:45" ht="130.44999999999999">
       <c r="B8" s="72" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="170" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D8" s="170" t="s">
         <v>62</v>
       </c>
       <c r="E8" s="170" t="s">
+        <v>221</v>
+      </c>
+      <c r="F8" s="170" t="s">
+        <v>222</v>
+      </c>
+      <c r="G8" s="170" t="s">
+        <v>223</v>
+      </c>
+      <c r="H8" s="170" t="s">
         <v>224</v>
       </c>
-      <c r="F8" s="170" t="s">
+      <c r="I8" s="170" t="s">
         <v>225</v>
       </c>
-      <c r="G8" s="170" t="s">
+      <c r="J8" s="170" t="s">
         <v>226</v>
       </c>
-      <c r="H8" s="170" t="s">
+      <c r="K8" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L8" s="28" t="s">
+        <v>319</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="N8" s="33" t="s">
         <v>227</v>
-      </c>
-      <c r="I8" s="170" t="s">
-        <v>228</v>
-      </c>
-      <c r="J8" s="170" t="s">
-        <v>229</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="L8" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="N8" s="33" t="s">
-        <v>231</v>
       </c>
       <c r="O8" s="41"/>
       <c r="P8" s="78"/>
       <c r="Q8" s="78"/>
       <c r="R8" s="199" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="9" spans="2:45" ht="68.25" thickBot="1">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="2:45" ht="65.25" thickBot="1">
       <c r="B9" s="74" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="171" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D9" s="171" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E9" s="171" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F9" s="171" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G9" s="171" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H9" s="171" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I9" s="171" t="s">
         <v>166</v>
       </c>
       <c r="J9" s="171" t="s">
+        <v>230</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="N9" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="K9" s="27" t="s">
+      <c r="O9" s="31" t="s">
         <v>235</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="M9" s="27" t="s">
-        <v>237</v>
-      </c>
-      <c r="N9" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="O9" s="31" t="s">
-        <v>239</v>
       </c>
       <c r="P9" s="146"/>
       <c r="Q9" s="76"/>
       <c r="R9" s="200" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="10" spans="2:45" ht="14.25" thickTop="1">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" spans="2:45" ht="13.6" thickTop="1">
       <c r="B10" s="213" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C10" s="172"/>
       <c r="D10" s="172"/>
@@ -44753,16 +44945,16 @@
       <c r="I10" s="172"/>
       <c r="J10" s="172"/>
       <c r="K10" s="201" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="L10" s="39" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M10" s="196" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="N10" s="215" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O10" s="202" t="s">
         <v>31</v>
@@ -44770,12 +44962,12 @@
       <c r="P10" s="42"/>
       <c r="Q10" s="42"/>
       <c r="R10" s="203" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="2:45">
       <c r="B11" s="213" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C11" s="173"/>
       <c r="D11" s="173"/>
@@ -44786,29 +44978,29 @@
       <c r="I11" s="173"/>
       <c r="J11" s="173"/>
       <c r="K11" s="204" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L11" s="39" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M11" s="196" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N11" s="216" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O11" s="40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P11" s="43"/>
       <c r="Q11" s="43"/>
       <c r="R11" s="205" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="2:45">
       <c r="B12" s="213" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C12" s="173"/>
       <c r="D12" s="173"/>
@@ -44819,19 +45011,19 @@
       <c r="I12" s="173"/>
       <c r="J12" s="173"/>
       <c r="K12" s="204" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L12" s="39" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M12" s="196" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="N12" s="216" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O12" s="40" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P12" s="43"/>
       <c r="Q12" s="43"/>
@@ -44841,7 +45033,7 @@
     </row>
     <row r="13" spans="2:45">
       <c r="B13" s="213" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C13" s="173"/>
       <c r="D13" s="173"/>
@@ -44852,29 +45044,29 @@
       <c r="I13" s="173"/>
       <c r="J13" s="173"/>
       <c r="K13" s="204" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L13" s="39" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M13" s="196" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N13" s="216" t="s">
         <v>32</v>
       </c>
       <c r="O13" s="40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P13" s="43"/>
       <c r="Q13" s="43"/>
       <c r="R13" s="205" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="2:45">
       <c r="B14" s="213" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C14" s="173"/>
       <c r="D14" s="173"/>
@@ -44885,29 +45077,29 @@
       <c r="I14" s="173"/>
       <c r="J14" s="173"/>
       <c r="K14" s="204" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L14" s="39" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M14" s="196" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N14" s="216" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="O14" s="40" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="P14" s="43"/>
       <c r="Q14" s="43"/>
       <c r="R14" s="205" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="2:45">
       <c r="B15" s="213" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C15" s="173"/>
       <c r="D15" s="173"/>
@@ -44918,29 +45110,29 @@
       <c r="I15" s="173"/>
       <c r="J15" s="173"/>
       <c r="K15" s="204" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L15" s="39" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M15" s="196" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="N15" s="216" t="s">
         <v>201</v>
       </c>
       <c r="O15" s="40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P15" s="43"/>
       <c r="Q15" s="43"/>
       <c r="R15" s="205" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="2:45">
       <c r="B16" s="213" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C16" s="173"/>
       <c r="D16" s="173"/>
@@ -44951,29 +45143,29 @@
       <c r="I16" s="173"/>
       <c r="J16" s="173"/>
       <c r="K16" s="204" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L16" s="39" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M16" s="196" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N16" s="216" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O16" s="40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P16" s="43"/>
       <c r="Q16" s="43"/>
       <c r="R16" s="205" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="2:18">
       <c r="B17" s="213" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C17" s="173"/>
       <c r="D17" s="173"/>
@@ -44984,29 +45176,29 @@
       <c r="I17" s="173"/>
       <c r="J17" s="173"/>
       <c r="K17" s="211" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L17" s="39" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M17" s="196" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="N17" s="239" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="O17" s="40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P17" s="43"/>
       <c r="Q17" s="43"/>
       <c r="R17" s="231" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" spans="2:18">
       <c r="B18" s="213" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C18" s="172"/>
       <c r="D18" s="172"/>
@@ -45017,16 +45209,16 @@
       <c r="I18" s="172"/>
       <c r="J18" s="172"/>
       <c r="K18" s="204" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L18" s="214" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M18" s="196" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="N18" s="215" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O18" s="202" t="s">
         <v>31</v>
@@ -45034,12 +45226,12 @@
       <c r="P18" s="42"/>
       <c r="Q18" s="42"/>
       <c r="R18" s="203" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="2:18">
       <c r="B19" s="213" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C19" s="173"/>
       <c r="D19" s="173"/>
@@ -45050,29 +45242,29 @@
       <c r="I19" s="173"/>
       <c r="J19" s="173"/>
       <c r="K19" s="220" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L19" s="214" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M19" s="196" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N19" s="216" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O19" s="40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P19" s="43"/>
       <c r="Q19" s="43"/>
       <c r="R19" s="205" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="2:18">
       <c r="B20" s="213" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C20" s="173"/>
       <c r="D20" s="173"/>
@@ -45083,19 +45275,19 @@
       <c r="I20" s="173"/>
       <c r="J20" s="173"/>
       <c r="K20" s="220" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L20" s="214" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M20" s="196" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="N20" s="216" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O20" s="40" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P20" s="43"/>
       <c r="Q20" s="43"/>
@@ -45105,7 +45297,7 @@
     </row>
     <row r="21" spans="2:18">
       <c r="B21" s="213" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C21" s="173"/>
       <c r="D21" s="173"/>
@@ -45116,29 +45308,29 @@
       <c r="I21" s="173"/>
       <c r="J21" s="173"/>
       <c r="K21" s="220" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L21" s="214" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M21" s="196" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="N21" s="216" t="s">
         <v>32</v>
       </c>
       <c r="O21" s="40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P21" s="43"/>
       <c r="Q21" s="43"/>
       <c r="R21" s="205" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="2:18">
       <c r="B22" s="213" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C22" s="173"/>
       <c r="D22" s="173"/>
@@ -45149,29 +45341,29 @@
       <c r="I22" s="173"/>
       <c r="J22" s="173"/>
       <c r="K22" s="220" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L22" s="214" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M22" s="196" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N22" s="216" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="O22" s="40" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="P22" s="43"/>
       <c r="Q22" s="43"/>
       <c r="R22" s="205" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23" spans="2:18">
       <c r="B23" s="213" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C23" s="173"/>
       <c r="D23" s="173"/>
@@ -45182,29 +45374,29 @@
       <c r="I23" s="173"/>
       <c r="J23" s="173"/>
       <c r="K23" s="220" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L23" s="214" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M23" s="196" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="N23" s="216" t="s">
         <v>201</v>
       </c>
       <c r="O23" s="40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P23" s="43"/>
       <c r="Q23" s="43"/>
       <c r="R23" s="205" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24" spans="2:18">
       <c r="B24" s="213" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C24" s="173"/>
       <c r="D24" s="173"/>
@@ -45215,29 +45407,29 @@
       <c r="I24" s="173"/>
       <c r="J24" s="173"/>
       <c r="K24" s="220" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L24" s="214" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M24" s="196" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N24" s="216" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O24" s="40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P24" s="43"/>
       <c r="Q24" s="43"/>
       <c r="R24" s="205" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="2:18">
       <c r="B25" s="213" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C25" s="173"/>
       <c r="D25" s="173"/>
@@ -45248,29 +45440,29 @@
       <c r="I25" s="173"/>
       <c r="J25" s="173"/>
       <c r="K25" s="220" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L25" s="214" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M25" s="196" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="N25" s="216" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="O25" s="40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P25" s="43"/>
       <c r="Q25" s="43"/>
       <c r="R25" s="205" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" spans="2:18">
       <c r="B26" s="213" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C26" s="172"/>
       <c r="D26" s="172"/>
@@ -45281,29 +45473,29 @@
       <c r="I26" s="172"/>
       <c r="J26" s="172"/>
       <c r="K26" s="204" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L26" s="39" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="M26" s="196" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="N26" s="216" t="s">
         <v>32</v>
       </c>
       <c r="O26" s="40" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="P26" s="43"/>
       <c r="Q26" s="43"/>
       <c r="R26" s="205" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="2:18">
       <c r="B27" s="213" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C27" s="173"/>
       <c r="D27" s="173"/>
@@ -45314,29 +45506,29 @@
       <c r="I27" s="173"/>
       <c r="J27" s="173"/>
       <c r="K27" s="220" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L27" s="39" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="M27" s="196" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="N27" s="216" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="O27" s="40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P27" s="43"/>
       <c r="Q27" s="43"/>
       <c r="R27" s="205" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="2:18">
       <c r="B28" s="213" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C28" s="173"/>
       <c r="D28" s="173"/>
@@ -45347,29 +45539,29 @@
       <c r="I28" s="173"/>
       <c r="J28" s="173"/>
       <c r="K28" s="220" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L28" s="39" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="M28" s="196" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="N28" s="216" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="O28" s="40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P28" s="43"/>
       <c r="Q28" s="43"/>
       <c r="R28" s="205" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18" ht="14.25" thickBot="1">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" ht="13.6" thickBot="1">
       <c r="B29" s="212" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C29" s="221"/>
       <c r="D29" s="221"/>
@@ -45380,24 +45572,24 @@
       <c r="I29" s="221"/>
       <c r="J29" s="221"/>
       <c r="K29" s="211" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L29" s="235" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="M29" s="234" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="N29" s="223" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O29" s="236" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P29" s="237"/>
       <c r="Q29" s="237"/>
       <c r="R29" s="238" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" spans="2:18">
@@ -46276,7 +46468,7 @@
     </row>
     <row r="91" spans="21:45">
       <c r="U91" s="206" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="V91" s="206"/>
       <c r="W91" s="206"/>
@@ -46311,28 +46503,31 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"Index,Matrix Search"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="14.25" thickBot="1">
+    <row r="2" spans="2:4" ht="13.6" thickBot="1">
       <c r="B2" s="85" t="s">
         <v>84</v>
       </c>
@@ -46342,7 +46537,7 @@
       </c>
       <c r="D2" s="86"/>
     </row>
-    <row r="3" spans="2:4" ht="14.25" thickBot="1">
+    <row r="3" spans="2:4" ht="13.6" thickBot="1">
       <c r="B3" s="79" t="s">
         <v>82</v>
       </c>
@@ -46353,7 +46548,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="14.25" thickTop="1">
+    <row r="4" spans="2:4" ht="13.6" thickTop="1">
       <c r="B4" s="13">
         <v>0</v>
       </c>
@@ -46364,7 +46559,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="40.5">
+    <row r="5" spans="2:4" ht="38.75">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -46375,7 +46570,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="27">
+    <row r="6" spans="2:4" ht="25.85">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -46386,7 +46581,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="54">
+    <row r="7" spans="2:4" ht="51.65">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -46397,7 +46592,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="81">
+    <row r="8" spans="2:4" ht="77.45">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -46408,7 +46603,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="41.25" customHeight="1">
+    <row r="9" spans="2:4" ht="41.3" customHeight="1">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -46419,7 +46614,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="27">
+    <row r="10" spans="2:4" ht="25.85">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -46430,7 +46625,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="27">
+    <row r="11" spans="2:4" ht="25.85">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -46441,7 +46636,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="27">
+    <row r="12" spans="2:4" ht="25.85">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -46452,7 +46647,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="27">
+    <row r="13" spans="2:4" ht="25.85">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -46463,7 +46658,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="27">
+    <row r="14" spans="2:4" ht="25.85">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -46474,7 +46669,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="135">
+    <row r="15" spans="2:4" ht="129.1">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -46496,7 +46691,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="27">
+    <row r="17" spans="2:4" ht="25.85">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -46507,7 +46702,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="67.5">
+    <row r="18" spans="2:4" ht="90.35">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -46518,7 +46713,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="40.5">
+    <row r="19" spans="2:4" ht="38.75">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -46529,7 +46724,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="64.5" customHeight="1">
+    <row r="20" spans="2:4" ht="64.55" customHeight="1">
       <c r="B20" s="2">
         <v>16</v>
       </c>
@@ -46551,26 +46746,26 @@
         <v>198</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="27">
+    <row r="22" spans="2:4" ht="25.85">
       <c r="B22" s="2">
         <v>18</v>
       </c>
       <c r="C22" s="89" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D22" s="91" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="27">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="25.85">
       <c r="B23" s="2">
         <v>19</v>
       </c>
       <c r="C23" s="89" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D23" s="91" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -46588,7 +46783,7 @@
       <c r="C26" s="89"/>
       <c r="D26" s="75"/>
     </row>
-    <row r="27" spans="2:4" ht="14.25" thickBot="1">
+    <row r="27" spans="2:4" ht="13.6" thickBot="1">
       <c r="B27" s="4"/>
       <c r="C27" s="90"/>
       <c r="D27" s="6"/>
@@ -46597,5 +46792,8 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_SLIP-CSTD-0-01-B-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_SLIP-CSTD-0-01-B-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\10_mcu\19epfv3_mcu_app_mainline\src\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC3019A-A1AF-4AD4-A2F0-AAA9BB966957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2DBD2E-C387-4295-96DA-1DD7401435AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7575" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14265" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="12" r:id="rId1"/>
@@ -674,7 +674,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2311" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2316" uniqueCount="343">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2946,13 +2946,6 @@
     <t>OPT</t>
   </si>
   <si>
-    <t>VSCW</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>○</t>
-  </si>
-  <si>
     <t>0b</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3068,9 +3061,6 @@
   <si>
     <t>MALFUNC</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VSCEXIST</t>
   </si>
   <si>
     <t>VSCEXIST</t>
@@ -3212,9 +3202,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>(株)NTTデータMSE</t>
-  </si>
-  <si>
     <t>承認</t>
     <rPh sb="0" eb="2">
       <t>ショウニン</t>
@@ -3347,6 +3334,35 @@
 [C_SLIP]シート
 ・数式の変更(AU8、AU10、AU11)</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(株)デンソー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1.0.2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DTPH Kiko</t>
+  </si>
+  <si>
+    <t>BEVシス検ADAS
+課題対応（BEV3CDCMET-2941）
+[Matrix]シート
+・RWの記載を変更（○→ー）
+[CH_Design]シート
+・RWの記載を変更（VSCW→ー）</t>
+    <rPh sb="11" eb="13">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>－</t>
   </si>
 </sst>
 </file>
@@ -3707,7 +3723,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="84">
+  <borders count="85">
     <border>
       <left/>
       <right/>
@@ -4792,6 +4808,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -4804,7 +4833,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="332">
+  <cellXfs count="337">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5591,6 +5620,21 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5600,6 +5644,9 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="76" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5639,9 +5686,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="82" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6146,16 +6190,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>100782</xdr:colOff>
+      <xdr:colOff>134399</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>100782</xdr:rowOff>
+      <xdr:rowOff>103957</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACDFDA46-25D6-4507-B30B-3B827B62A21E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{538B1B2D-D26E-DEDE-93DD-B5503616FE11}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6171,8 +6215,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5667375" y="8420100"/>
-          <a:ext cx="586557" cy="586557"/>
+          <a:off x="5098676" y="8157882"/>
+          <a:ext cx="571429" cy="571429"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10142,17 +10186,17 @@
       <sheetName val="４．ナビモデル"/>
       <sheetName val="３．サウンドモデル"/>
       <sheetName val="２．ラジオモデル"/>
+      <sheetName val="1.概述"/>
       <sheetName val="V200複合試験_担当分け_(2)1"/>
       <sheetName val="Spec_List_(19MC-DCM)_1"/>
       <sheetName val="Cooling_Unit"/>
-      <sheetName val="1.概述"/>
       <sheetName val="OpenIssueList"/>
-      <sheetName val="PullDown"/>
       <sheetName val="ECU基盤"/>
       <sheetName val="Name2"/>
       <sheetName val="Name3"/>
       <sheetName val="Company"/>
       <sheetName val="Name"/>
+      <sheetName val="PullDown"/>
       <sheetName val="エンジン型式"/>
       <sheetName val="分类数据"/>
       <sheetName val="index"/>
@@ -10184,6 +10228,37 @@
       <sheetName val="改訂履歴"/>
       <sheetName val="Sheet1"/>
       <sheetName val="⑥フューエル"/>
+      <sheetName val="STEP1-Definition"/>
+      <sheetName val="No.31"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="测试计划"/>
+      <sheetName val="2.2.4_起動終了時"/>
+      <sheetName val="全戻りﾊﾞｸﾞ"/>
+      <sheetName val="DataShare"/>
+      <sheetName val="ＯＰＭ設備"/>
+      <sheetName val="償却計算"/>
+      <sheetName val="技術費"/>
+      <sheetName val="消耗材"/>
+      <sheetName val="生産用消耗工具費"/>
+      <sheetName val="投資込みＭＪ原価"/>
+      <sheetName val="ＭＪ加工費"/>
+      <sheetName val="仕損根拠"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="ERRＩＤ90"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="調査シート"/>
+      <sheetName val="SCH"/>
+      <sheetName val="发行控制"/>
+      <sheetName val="Vibrate test"/>
+      <sheetName val="Data"/>
+      <sheetName val="注釈"/>
+      <sheetName val="仕向け決定用情報取得(GM250)"/>
+      <sheetName val="付録①（GM用）"/>
+      <sheetName val="Data.Share"/>
+      <sheetName val="Func.Share"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -10264,10 +10339,10 @@
       <sheetData sheetId="57" refreshError="1"/>
       <sheetData sheetId="58" refreshError="1"/>
       <sheetData sheetId="59" refreshError="1"/>
-      <sheetData sheetId="60"/>
+      <sheetData sheetId="60" refreshError="1"/>
       <sheetData sheetId="61"/>
       <sheetData sheetId="62"/>
-      <sheetData sheetId="63" refreshError="1"/>
+      <sheetData sheetId="63"/>
       <sheetData sheetId="64" refreshError="1"/>
       <sheetData sheetId="65" refreshError="1"/>
       <sheetData sheetId="66" refreshError="1"/>
@@ -10306,6 +10381,37 @@
       <sheetData sheetId="99" refreshError="1"/>
       <sheetData sheetId="100" refreshError="1"/>
       <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10444,12 +10550,49 @@
       <sheetName val="Config - dspmgr"/>
       <sheetName val="凡例・注記記載用"/>
       <sheetName val="入力パラメータ"/>
-      <sheetName val="原紙"/>
       <sheetName val="マスタテーブル登録データ"/>
       <sheetName val="記入シート"/>
+      <sheetName val="原紙"/>
       <sheetName val="format"/>
       <sheetName val="検査シート"/>
       <sheetName val="1.概述"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="集計表"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="Defined Layout Screen_Ver.0.6"/>
+      <sheetName val="ｲﾝﾊﾟｸﾄ影響台数集計表"/>
+      <sheetName val="実勢(売上)台数表"/>
+      <sheetName val="月別企画台数表"/>
+      <sheetName val="プロジェクト一覧表(現行)"/>
+      <sheetName val="限界利益表(半期別)"/>
+      <sheetName val="機種マスタ"/>
+      <sheetName val="機種ﾏｽﾀ（他車）"/>
+      <sheetName val="売上高表(半期別)"/>
+      <sheetName val="地点情報データ応答"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="リソーセス算出"/>
+      <sheetName val="定義"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="変更区分一覧"/>
+      <sheetName val="難易度量一覧"/>
+      <sheetName val="ユーザ一覧"/>
+      <sheetName val="Normal(Mark)"/>
+      <sheetName val="リストデータ"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="入力規則"/>
+      <sheetName val="#REF"/>
+      <sheetName val="Contents"/>
+      <sheetName val="選択肢"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -10593,6 +10736,43 @@
       <sheetData sheetId="132" refreshError="1"/>
       <sheetData sheetId="133" refreshError="1"/>
       <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
+      <sheetData sheetId="141" refreshError="1"/>
+      <sheetData sheetId="142" refreshError="1"/>
+      <sheetData sheetId="143" refreshError="1"/>
+      <sheetData sheetId="144" refreshError="1"/>
+      <sheetData sheetId="145" refreshError="1"/>
+      <sheetData sheetId="146" refreshError="1"/>
+      <sheetData sheetId="147" refreshError="1"/>
+      <sheetData sheetId="148" refreshError="1"/>
+      <sheetData sheetId="149" refreshError="1"/>
+      <sheetData sheetId="150" refreshError="1"/>
+      <sheetData sheetId="151" refreshError="1"/>
+      <sheetData sheetId="152" refreshError="1"/>
+      <sheetData sheetId="153" refreshError="1"/>
+      <sheetData sheetId="154" refreshError="1"/>
+      <sheetData sheetId="155" refreshError="1"/>
+      <sheetData sheetId="156" refreshError="1"/>
+      <sheetData sheetId="157" refreshError="1"/>
+      <sheetData sheetId="158" refreshError="1"/>
+      <sheetData sheetId="159" refreshError="1"/>
+      <sheetData sheetId="160" refreshError="1"/>
+      <sheetData sheetId="161" refreshError="1"/>
+      <sheetData sheetId="162" refreshError="1"/>
+      <sheetData sheetId="163" refreshError="1"/>
+      <sheetData sheetId="164" refreshError="1"/>
+      <sheetData sheetId="165" refreshError="1"/>
+      <sheetData sheetId="166" refreshError="1"/>
+      <sheetData sheetId="167" refreshError="1"/>
+      <sheetData sheetId="168" refreshError="1"/>
+      <sheetData sheetId="169" refreshError="1"/>
+      <sheetData sheetId="170" refreshError="1"/>
+      <sheetData sheetId="171" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10774,10 +10954,10 @@
       <sheetName val="CPF"/>
       <sheetName val="編集"/>
       <sheetName val="PAIData"/>
+      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="NCastalone"/>
       <sheetName val="dongia (2)"/>
       <sheetName val="Volumes"/>
-      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="加工費"/>
       <sheetName val="車両仕様 嗼1嗼1噌1鲌"/>
       <sheetName val="車両仕様 勜+勜+匬+鲌"/>
@@ -10787,8 +10967,8 @@
       <sheetName val="Y230"/>
       <sheetName val="MASTER"/>
       <sheetName val="設定"/>
+      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="⑥フューエル"/>
-      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ"/>
       <sheetName val="設品表01-3-23作成"/>
       <sheetName val="wire"/>
@@ -10804,25 +10984,24 @@
       <sheetName val="610L611L品番一覧"/>
       <sheetName val="【Input】見積基礎情報（海外生産分)"/>
       <sheetName val="IM-P-L-JB "/>
-      <sheetName val="797T輸入部品リスト"/>
-      <sheetName val="テーブル"/>
-      <sheetName val="Master Updated(517)"/>
-      <sheetName val="４-２．151項目累積（日本）"/>
-      <sheetName val="５-２．151項目累積（北米）"/>
-      <sheetName val="５-１．151項目詳細（北米）"/>
-      <sheetName val="545N仕様ﾗﾌ2"/>
-      <sheetName val="商品力向上"/>
-      <sheetName val="OP-PD"/>
-      <sheetName val="６２３Ｔ"/>
+      <sheetName val="RMBSS's Triggered"/>
+      <sheetName val="_"/>
       <sheetName val="Main 2"/>
       <sheetName val="Datasheet from R. Hinds"/>
-      <sheetName val="GMT900 IPC"/>
+      <sheetName val="545N仕様ﾗﾌ2"/>
+      <sheetName val="Master Updated(517)"/>
+      <sheetName val="６２３Ｔ"/>
+      <sheetName val="商品力向上"/>
+      <sheetName val="ED AND EDOV"/>
       <sheetName val="HORAS_TRAB"/>
       <sheetName val="Resumo_Corolla"/>
       <sheetName val="GASTOS_COROLLA"/>
-      <sheetName val="CALC"/>
-      <sheetName val="ﾘｽﾄ候補"/>
-      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="④要素記号一覧表"/>
+      <sheetName val="START"/>
+      <sheetName val="Blue Flag"/>
+      <sheetName val="Calc Sheet Budget"/>
+      <sheetName val="見積一覧（１案）"/>
+      <sheetName val="部品"/>
       <sheetName val="①評価項目_メーカー"/>
       <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0011__x00"/>
       <sheetName val="車両仕様4__x005f_x0000__x005f_x0011__x005f_x0000_"/>
@@ -10849,16 +11028,9 @@
       <sheetName val="車両仕様_4___x005f_x005f_x005f_x005f_x005f_x005f_x001"/>
       <sheetName val="車両仕様4___x005f_x005f_x005f_x005f_x005f_x005f_x0011"/>
       <sheetName val="EFFY_MAZDA"/>
-      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
-      <sheetName val="_"/>
-      <sheetName val="RMBSS's Triggered"/>
-      <sheetName val="ED AND EDOV"/>
-      <sheetName val="④要素記号一覧表"/>
-      <sheetName val="START"/>
-      <sheetName val="Blue Flag"/>
-      <sheetName val="Calc Sheet Budget"/>
-      <sheetName val="見積一覧（１案）"/>
-      <sheetName val="部品"/>
+      <sheetName val="４-２．151項目累積（日本）"/>
+      <sheetName val="５-２．151項目累積（北米）"/>
+      <sheetName val="５-１．151項目詳細（北米）"/>
       <sheetName val="sebelumCR"/>
       <sheetName val="08TMME"/>
       <sheetName val="VCPT"/>
@@ -10868,6 +11040,14 @@
       <sheetName val="WIP Cal Sheet"/>
       <sheetName val="Pricing overview"/>
       <sheetName val="駆動系1"/>
+      <sheetName val="797T輸入部品リスト"/>
+      <sheetName val="テーブル"/>
+      <sheetName val="OP-PD"/>
+      <sheetName val="GMT900 IPC"/>
+      <sheetName val="CALC"/>
+      <sheetName val="ﾘｽﾄ候補"/>
+      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
       <sheetName val="393.N"/>
       <sheetName val="CæÊ _x0015_ Op"/>
       <sheetName val="ƒƒCƒ“‰æ–Ê _x0015_ Op"/>
@@ -10887,6 +11067,10 @@
       <sheetName val="車両仕様_ᵣ逰ᵣ邀ᵣ郰ᵣ"/>
       <sheetName val="他"/>
       <sheetName val="part"/>
+      <sheetName val="415T原"/>
+      <sheetName val="PAC14"/>
+      <sheetName val="部品表"/>
+      <sheetName val="■07中期明細雛形"/>
       <sheetName val="Vectra"/>
       <sheetName val="PRADO"/>
       <sheetName val="Previous"/>
@@ -10926,10 +11110,6 @@
       <sheetName val="OTHERS x620"/>
       <sheetName val="Ref"/>
       <sheetName val="TOTAL P2"/>
-      <sheetName val="415T原"/>
-      <sheetName val="PAC14"/>
-      <sheetName val="部品表"/>
-      <sheetName val="■07中期明細雛形"/>
       <sheetName val="BUYERS"/>
       <sheetName val="Status"/>
       <sheetName val="PR"/>
@@ -11917,18 +12097,18 @@
       <sheetName val="SUM"/>
       <sheetName val="ﾄﾗｯｸ"/>
       <sheetName val="00"/>
+      <sheetName val="追加検討（調光外部出力）"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="option"/>
       <sheetName val="課題管理"/>
       <sheetName val="C-55227AB"/>
       <sheetName val="Data Definition"/>
       <sheetName val="FC_まとめる"/>
-      <sheetName val="vocabulary"/>
-      <sheetName val="Calibration"/>
-      <sheetName val="CVBS"/>
-      <sheetName val="RGB"/>
       <sheetName val="車両仕様_4___x0011__x00"/>
       <sheetName val="ドメインリスト"/>
-      <sheetName val="option"/>
-      <sheetName val="追加検討（調光外部出力）"/>
       <sheetName val="入力規則"/>
       <sheetName val="Inf"/>
       <sheetName val="#REF!"/>
@@ -12019,8 +12199,29 @@
       <sheetName val="入力LIST"/>
       <sheetName val="パラメータ一覧(AXSS.AXCS)"/>
       <sheetName val="設定値定義"/>
+      <sheetName val="リストデータ"/>
+      <sheetName val="All"/>
+      <sheetName val="58831-06360"/>
+      <sheetName val="1999.4"/>
+      <sheetName val="車両仕様 _x005f_x0000__x005f_x0000__x005f_x000a__x000"/>
+      <sheetName val="車両仕様_x005f_x0000_ῃ_x005f_x0000__x005f_x0014__x000"/>
+      <sheetName val="車両仕様_x005f_x0000__x005f_x0000__x005f_x0000__x0000"/>
+      <sheetName val="車両仕様_x005f_x0000_ῆ玐ῆꆠῨ"/>
+      <sheetName val="車両仕様4?_x005f_x0000__x005f_x0000__x005f_x0000_"/>
+      <sheetName val="SHEET  car no"/>
       <sheetName val="車両仕様????帅?"/>
       <sheetName val="Net Price Position _ Sheet 1"/>
+      <sheetName val="Packing_List2"/>
+      <sheetName val="Packing_List"/>
+      <sheetName val="Calculation_PS"/>
+      <sheetName val="Customer_behaver"/>
+      <sheetName val="Seat_Assy_Tool_Tracking"/>
+      <sheetName val="Stock_in_Trade1"/>
+      <sheetName val="Packing_List21"/>
+      <sheetName val="Packing_List1"/>
+      <sheetName val="Calculation_PS1"/>
+      <sheetName val="Customer_behaver1"/>
+      <sheetName val="Seat_Assy_Tool_Tracking1"/>
       <sheetName val="POs"/>
       <sheetName val="計算式"/>
       <sheetName val="工管合計"/>
@@ -13544,15 +13745,9 @@
       <sheetName val="5"/>
       <sheetName val="確認ｼｰﾄ(TBU)"/>
       <sheetName val="Sheet1 (2)"/>
-      <sheetName val="SHEET  car no"/>
       <sheetName val="サイクル"/>
       <sheetName val="特殊サイクル一覧"/>
       <sheetName val="カメラ"/>
-      <sheetName val="車両仕様 _x005f_x0000__x005f_x0000__x005f_x000a__x000"/>
-      <sheetName val="車両仕様_x005f_x0000_ῃ_x005f_x0000__x005f_x0014__x000"/>
-      <sheetName val="車両仕様_x005f_x0000__x005f_x0000__x005f_x0000__x0000"/>
-      <sheetName val="車両仕様_x005f_x0000_ῆ玐ῆꆠῨ"/>
-      <sheetName val="車両仕様4?_x005f_x0000__x005f_x0000__x005f_x0000_"/>
       <sheetName val="台数"/>
       <sheetName val="MET397D-25"/>
       <sheetName val="集計表"/>
@@ -13561,21 +13756,6 @@
       <sheetName val="Ｓｉ問連"/>
       <sheetName val="アップロード系(2)"/>
       <sheetName val="エンジン型式"/>
-      <sheetName val="リストデータ"/>
-      <sheetName val="All"/>
-      <sheetName val="58831-06360"/>
-      <sheetName val="1999.4"/>
-      <sheetName val="Packing_List2"/>
-      <sheetName val="Packing_List"/>
-      <sheetName val="Calculation_PS"/>
-      <sheetName val="Customer_behaver"/>
-      <sheetName val="Seat_Assy_Tool_Tracking"/>
-      <sheetName val="Stock_in_Trade1"/>
-      <sheetName val="Packing_List21"/>
-      <sheetName val="Packing_List1"/>
-      <sheetName val="Calculation_PS1"/>
-      <sheetName val="Customer_behaver1"/>
-      <sheetName val="Seat_Assy_Tool_Tracking1"/>
       <sheetName val="Index"/>
       <sheetName val="Defined Layout Screen_Ver.0.6"/>
       <sheetName val="９ｘ"/>
@@ -13587,6 +13767,185 @@
       <sheetName val="config"/>
       <sheetName val="地点情報データ応答"/>
       <sheetName val="Par"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="ETC機能判定"/>
+      <sheetName val="ETCメニュー"/>
+      <sheetName val="登録情報表示"/>
+      <sheetName val="ETC設定"/>
+      <sheetName val="履歴情報表示"/>
+      <sheetName val="履歴情報詳細表示"/>
+      <sheetName val="メニュー２"/>
+      <sheetName val="割込み(Disp)"/>
+      <sheetName val="割込み(Navi)"/>
+      <sheetName val="走行強制状態変化"/>
+      <sheetName val="入力パラメータ"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="リスト画面"/>
+      <sheetName val="特殊画面"/>
+      <sheetName val="入力画面"/>
+      <sheetName val="メッセージ受信開始"/>
+      <sheetName val="Mark"/>
+      <sheetName val="Contents"/>
+      <sheetName val="車両仕様4_ "/>
+      <sheetName val="改正履歴"/>
+      <sheetName val="リスト選択用"/>
+      <sheetName val="变更履历"/>
+      <sheetName val="Menu List"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="検査シート"/>
+      <sheetName val="Cover"/>
+      <sheetName val="MIS REPORT "/>
+      <sheetName val="（別紙5-1）PP02簡素化"/>
+      <sheetName val="universal"/>
+      <sheetName val="Cost Casting"/>
+      <sheetName val="paint mtrl"/>
+      <sheetName val="corolla_095W_"/>
+      <sheetName val="dyna"/>
+      <sheetName val="FC"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="ﾕｰｻﾞｰ設定"/>
+      <sheetName val="同行评审"/>
+      <sheetName val="5.心配点抽出-0"/>
+      <sheetName val="0.表紙"/>
+      <sheetName val="1._概要"/>
+      <sheetName val="4 選局"/>
+      <sheetName val="定数"/>
+      <sheetName val="Case 21_1"/>
+      <sheetName val="96期(川崎)"/>
+      <sheetName val="ORDSHP"/>
+      <sheetName val="B"/>
+      <sheetName val="Blue_Flag3"/>
+      <sheetName val="Calc_Sheet_Budget3"/>
+      <sheetName val="_PART_479W_LHD3"/>
+      <sheetName val="_PART_MYY5A3"/>
+      <sheetName val="393_N3"/>
+      <sheetName val="WIP_Cal_Sheet3"/>
+      <sheetName val="Pricing_overview3"/>
+      <sheetName val="Lookup_Table3"/>
+      <sheetName val="promo_lists_20113"/>
+      <sheetName val="車両仕様_嗼1嗼1噌1鲌3"/>
+      <sheetName val="車両仕様_勜+勜+匬+鲌3"/>
+      <sheetName val="EquipmentTrimming_Cabin_NS3"/>
+      <sheetName val="Reference_3"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000_?_x005f_x0012_?瞳?3"/>
+      <sheetName val="車両仕様_???_x005f_x0012_?瞳?3"/>
+      <sheetName val="160th_NPCC_Nov'103"/>
+      <sheetName val="RMBSS's_Triggered3"/>
+      <sheetName val="車両仕様?4???_??3"/>
+      <sheetName val="車両仕様_???_?瞳?3"/>
+      <sheetName val="車両仕様???ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様?4??_?3"/>
+      <sheetName val="車両仕様4??_?3"/>
+      <sheetName val="車両仕様____瞳_3"/>
+      <sheetName val="車両仕様______瞳_3"/>
+      <sheetName val="車両仕様_4______3"/>
+      <sheetName val="車両仕様___ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様_4____3"/>
+      <sheetName val="車両仕様4____3"/>
+      <sheetName val="PRICE_LIST3"/>
+      <sheetName val="Loss_Time3"/>
+      <sheetName val="Price_range_IT3"/>
+      <sheetName val="Avensis+d_seg__in_&amp;_out_of_UK+3"/>
+      <sheetName val="#ofclose__xl3"/>
+      <sheetName val="Annexes_toutes_bases3"/>
+      <sheetName val="DON_GIA3"/>
+      <sheetName val="CHITIET_VL-NC3"/>
+      <sheetName val="TONGKE3p_3"/>
+      <sheetName val="TOTAL_P23"/>
+      <sheetName val="2_-_Summary3"/>
+      <sheetName val="IPOTESI_PIANO_STATICA3"/>
+      <sheetName val="make_up3"/>
+      <sheetName val="車両仕様_???_x005f_x005f_x005f_x0012_?瞳?3"/>
+      <sheetName val="調達担当者(06_2～)3"/>
+      <sheetName val="車両仕様__x005f_x0000__2"/>
+      <sheetName val="車両仕様_x005f_x0000__N2"/>
+      <sheetName val="車両仕様___x005f_x0012_2"/>
+      <sheetName val="車両仕様__x005f_x005f_x2"/>
+      <sheetName val="車両仕様___x005f_x005f_2"/>
+      <sheetName val="05-065_she2"/>
+      <sheetName val="idgr_-_formula2"/>
+      <sheetName val="IDGR_(3)2"/>
+      <sheetName val="IDGR_(2)2"/>
+      <sheetName val="PLIV_(3)2"/>
+      <sheetName val="PLIV_(2)2"/>
+      <sheetName val="PLIV_(template)2"/>
+      <sheetName val="inv_recon2"/>
+      <sheetName val="side_member2"/>
+      <sheetName val="TTC_(FG)2"/>
+      <sheetName val="Sheet1_(3)2"/>
+      <sheetName val="truck_allocation2"/>
+      <sheetName val="Supplier_Price_Check2"/>
+      <sheetName val="$_-_june2"/>
+      <sheetName val="Vios_Cost_Reduction_actual_pro2"/>
+      <sheetName val="RET_PALLET2"/>
+      <sheetName val="Form_A2"/>
+      <sheetName val="NG_SUMMARY2"/>
+      <sheetName val="impact_pallet_and_racks2"/>
+      <sheetName val="Daily_WSD2"/>
+      <sheetName val="ass'y_12'04-05'053"/>
+      <sheetName val="Type_I2"/>
+      <sheetName val="Schedule_PM2"/>
+      <sheetName val="training_forklift2"/>
+      <sheetName val="Budget_by_Category2"/>
+      <sheetName val="investment_tmc_v8_0_34p2"/>
+      <sheetName val="PTD_Activity2"/>
+      <sheetName val="Sample_1PP_2"/>
+      <sheetName val="Open_Ran3"/>
+      <sheetName val="Open_RAN_23"/>
+      <sheetName val="CHIA_KH2"/>
+      <sheetName val="Purch__BP2"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0013"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0053"/>
+      <sheetName val="ＰＲＥ_NO1"/>
+      <sheetName val="Courier_4x2"/>
+      <sheetName val="Price_Trend2"/>
+      <sheetName val="車両仕様_?_x005f_x0012_?瞳?2"/>
+      <sheetName val="YARIS_HB2"/>
+      <sheetName val="00_KS"/>
+      <sheetName val="PRADO_3Dr_fl2"/>
+      <sheetName val="01_DATA2"/>
+      <sheetName val="Quality_Update2"/>
+      <sheetName val="prior_data"/>
+      <sheetName val="Table_Master"/>
+      <sheetName val="1_概述"/>
+      <sheetName val="Drop-down_Menu_List"/>
+      <sheetName val="Open_Item_List"/>
+      <sheetName val="本修正_DIFF_"/>
+      <sheetName val="Sector_Assignment"/>
+      <sheetName val="BQ_CONVEYOR"/>
+      <sheetName val="IMV_LIST_2003"/>
+      <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0000___x0"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000____瞳_"/>
+      <sheetName val="Part_list"/>
+      <sheetName val="INACT797"/>
+      <sheetName val="M1A"/>
+      <sheetName val="OK"/>
+      <sheetName val="??? Pilling upu_S y"/>
+      <sheetName val="ASF INVENTORY"/>
+      <sheetName val="車両仕様_4___x005f_x0013__x0013__x0013__x0013__x0013_"/>
+      <sheetName val="ጀጀ؀ԀЀࠀ᐀Ѐऀ܀̀܀ഀ܀Ԁऀ଀ࠀ_x0000_"/>
+      <sheetName val="CTable"/>
+      <sheetName val="bs is"/>
+      <sheetName val="成績"/>
+      <sheetName val="IT Checklist"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="No.31"/>
+      <sheetName val="コマンド認識, DTMF"/>
+      <sheetName val="CS2_SmcDriverインテグ項目"/>
+      <sheetName val="標準仕様DB"/>
+      <sheetName val="BEEP設定"/>
+      <sheetName val="休日"/>
+      <sheetName val="工数ｺｰﾄﾞﾘｽﾄ"/>
+      <sheetName val="5．キー入力動作説明"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="試験項目_R3小"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -14142,33 +14501,45 @@
       <sheetData sheetId="304" refreshError="1"/>
       <sheetData sheetId="305" refreshError="1"/>
       <sheetData sheetId="306" refreshError="1"/>
-      <sheetData sheetId="307">
+      <sheetData sheetId="307" refreshError="1"/>
+      <sheetData sheetId="308" refreshError="1"/>
+      <sheetData sheetId="309" refreshError="1"/>
+      <sheetData sheetId="310" refreshError="1"/>
+      <sheetData sheetId="311">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="308">
+      <sheetData sheetId="312">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="309">
+      <sheetData sheetId="313">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="310"/>
-      <sheetData sheetId="311"/>
-      <sheetData sheetId="312" refreshError="1"/>
-      <sheetData sheetId="313" refreshError="1"/>
-      <sheetData sheetId="314" refreshError="1"/>
-      <sheetData sheetId="315" refreshError="1"/>
+      <sheetData sheetId="314">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="315">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="316" refreshError="1"/>
       <sheetData sheetId="317" refreshError="1"/>
       <sheetData sheetId="318" refreshError="1"/>
@@ -15740,8 +16111,8 @@
       </sheetData>
       <sheetData sheetId="793">
         <row r="1">
-          <cell r="B1" t="str">
-            <v>1</v>
+          <cell r="A1" t="str">
+            <v>ﾄﾖﾀ自動車株式会社　調達本部　</v>
           </cell>
         </row>
       </sheetData>
@@ -15777,7 +16148,13 @@
       <sheetData sheetId="805" refreshError="1"/>
       <sheetData sheetId="806" refreshError="1"/>
       <sheetData sheetId="807" refreshError="1"/>
-      <sheetData sheetId="808"/>
+      <sheetData sheetId="808">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="809" refreshError="1"/>
       <sheetData sheetId="810" refreshError="1"/>
       <sheetData sheetId="811" refreshError="1"/>
@@ -16740,9 +17117,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1050">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -16964,9 +17341,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1082">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -16985,9 +17362,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1085">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17314,9 +17691,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1132">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17405,9 +17782,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1145">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17636,16 +18013,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1178">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1179">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17685,9 +18062,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1185">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17713,9 +18090,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1189">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17734,9 +18111,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1192">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17804,9 +18181,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1202">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17825,16 +18202,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1205">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1206">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17846,16 +18223,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1208">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1209">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17895,9 +18272,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1215">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17923,9 +18300,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1219">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17944,9 +18321,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1222">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18014,9 +18391,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1232">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18035,16 +18412,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1235">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1236">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18056,16 +18433,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1238">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1239">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18105,16 +18482,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1245">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1246">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -18174,16 +18551,76 @@
       <sheetData sheetId="1294"/>
       <sheetData sheetId="1295" refreshError="1"/>
       <sheetData sheetId="1296" refreshError="1"/>
-      <sheetData sheetId="1297"/>
-      <sheetData sheetId="1298"/>
-      <sheetData sheetId="1299"/>
-      <sheetData sheetId="1300"/>
-      <sheetData sheetId="1301"/>
-      <sheetData sheetId="1302"/>
-      <sheetData sheetId="1303"/>
-      <sheetData sheetId="1304"/>
-      <sheetData sheetId="1305"/>
-      <sheetData sheetId="1306"/>
+      <sheetData sheetId="1297">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1298">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1299">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1300">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1301">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1302">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1303">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1304">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1305">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1306">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1307" refreshError="1"/>
       <sheetData sheetId="1308" refreshError="1"/>
       <sheetData sheetId="1309" refreshError="1"/>
@@ -18193,13 +18630,13 @@
       <sheetData sheetId="1313" refreshError="1"/>
       <sheetData sheetId="1314" refreshError="1"/>
       <sheetData sheetId="1315" refreshError="1"/>
-      <sheetData sheetId="1316"/>
+      <sheetData sheetId="1316" refreshError="1"/>
       <sheetData sheetId="1317" refreshError="1"/>
       <sheetData sheetId="1318" refreshError="1"/>
       <sheetData sheetId="1319" refreshError="1"/>
       <sheetData sheetId="1320" refreshError="1"/>
       <sheetData sheetId="1321" refreshError="1"/>
-      <sheetData sheetId="1322" refreshError="1"/>
+      <sheetData sheetId="1322"/>
       <sheetData sheetId="1323" refreshError="1"/>
       <sheetData sheetId="1324" refreshError="1"/>
       <sheetData sheetId="1325" refreshError="1"/>
@@ -18294,39 +18731,33 @@
       <sheetData sheetId="1414" refreshError="1"/>
       <sheetData sheetId="1415" refreshError="1"/>
       <sheetData sheetId="1416" refreshError="1"/>
-      <sheetData sheetId="1417"/>
+      <sheetData sheetId="1417" refreshError="1"/>
       <sheetData sheetId="1418" refreshError="1"/>
       <sheetData sheetId="1419" refreshError="1"/>
       <sheetData sheetId="1420" refreshError="1"/>
       <sheetData sheetId="1421" refreshError="1"/>
       <sheetData sheetId="1422" refreshError="1"/>
-      <sheetData sheetId="1423"/>
-      <sheetData sheetId="1424"/>
-      <sheetData sheetId="1425"/>
-      <sheetData sheetId="1426"/>
+      <sheetData sheetId="1423" refreshError="1"/>
+      <sheetData sheetId="1424" refreshError="1"/>
+      <sheetData sheetId="1425" refreshError="1"/>
+      <sheetData sheetId="1426" refreshError="1"/>
       <sheetData sheetId="1427"/>
-      <sheetData sheetId="1428"/>
+      <sheetData sheetId="1428" refreshError="1"/>
       <sheetData sheetId="1429"/>
       <sheetData sheetId="1430"/>
       <sheetData sheetId="1431"/>
       <sheetData sheetId="1432"/>
       <sheetData sheetId="1433"/>
-      <sheetData sheetId="1434" refreshError="1"/>
-      <sheetData sheetId="1435">
-        <row r="3">
-          <cell r="C3" t="str">
-            <v>2022年</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1434"/>
+      <sheetData sheetId="1435"/>
       <sheetData sheetId="1436"/>
       <sheetData sheetId="1437"/>
       <sheetData sheetId="1438"/>
       <sheetData sheetId="1439"/>
-      <sheetData sheetId="1440"/>
-      <sheetData sheetId="1441"/>
-      <sheetData sheetId="1442"/>
-      <sheetData sheetId="1443"/>
+      <sheetData sheetId="1440" refreshError="1"/>
+      <sheetData sheetId="1441" refreshError="1"/>
+      <sheetData sheetId="1442" refreshError="1"/>
+      <sheetData sheetId="1443" refreshError="1"/>
       <sheetData sheetId="1444"/>
       <sheetData sheetId="1445"/>
       <sheetData sheetId="1446"/>
@@ -18338,8 +18769,14 @@
       <sheetData sheetId="1452"/>
       <sheetData sheetId="1453"/>
       <sheetData sheetId="1454"/>
-      <sheetData sheetId="1455"/>
-      <sheetData sheetId="1456"/>
+      <sheetData sheetId="1455" refreshError="1"/>
+      <sheetData sheetId="1456">
+        <row r="3">
+          <cell r="C3" t="str">
+            <v>2022年</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1457"/>
       <sheetData sheetId="1458"/>
       <sheetData sheetId="1459"/>
@@ -18419,19 +18856,73 @@
       <sheetData sheetId="1533"/>
       <sheetData sheetId="1534"/>
       <sheetData sheetId="1535"/>
-      <sheetData sheetId="1536"/>
-      <sheetData sheetId="1537"/>
+      <sheetData sheetId="1536">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1537">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1538"/>
-      <sheetData sheetId="1539"/>
+      <sheetData sheetId="1539">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1540"/>
-      <sheetData sheetId="1541"/>
-      <sheetData sheetId="1542"/>
-      <sheetData sheetId="1543"/>
+      <sheetData sheetId="1541">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1542">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1543">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1544"/>
-      <sheetData sheetId="1545"/>
+      <sheetData sheetId="1545">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1546"/>
-      <sheetData sheetId="1547"/>
-      <sheetData sheetId="1548"/>
+      <sheetData sheetId="1547">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1548">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1549"/>
       <sheetData sheetId="1550"/>
       <sheetData sheetId="1551"/>
@@ -19821,52 +20312,52 @@
       <sheetData sheetId="2935"/>
       <sheetData sheetId="2936"/>
       <sheetData sheetId="2937"/>
-      <sheetData sheetId="2938">
-        <row r="1">
-          <cell r="A1"/>
-        </row>
-      </sheetData>
+      <sheetData sheetId="2938"/>
       <sheetData sheetId="2939"/>
       <sheetData sheetId="2940"/>
       <sheetData sheetId="2941"/>
-      <sheetData sheetId="2942" refreshError="1"/>
-      <sheetData sheetId="2943">
+      <sheetData sheetId="2942"/>
+      <sheetData sheetId="2943"/>
+      <sheetData sheetId="2944"/>
+      <sheetData sheetId="2945"/>
+      <sheetData sheetId="2946"/>
+      <sheetData sheetId="2947"/>
+      <sheetData sheetId="2948"/>
+      <sheetData sheetId="2949"/>
+      <sheetData sheetId="2950"/>
+      <sheetData sheetId="2951"/>
+      <sheetData sheetId="2952"/>
+      <sheetData sheetId="2953"/>
+      <sheetData sheetId="2954"/>
+      <sheetData sheetId="2955"/>
+      <sheetData sheetId="2956"/>
+      <sheetData sheetId="2957"/>
+      <sheetData sheetId="2958"/>
+      <sheetData sheetId="2959">
+        <row r="1">
+          <cell r="A1"/>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2960"/>
+      <sheetData sheetId="2961"/>
+      <sheetData sheetId="2962"/>
+      <sheetData sheetId="2963">
         <row r="1">
           <cell r="B1" t="str">
             <v>文章管理番号</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2944"/>
-      <sheetData sheetId="2945" refreshError="1"/>
-      <sheetData sheetId="2946" refreshError="1"/>
-      <sheetData sheetId="2947" refreshError="1"/>
-      <sheetData sheetId="2948" refreshError="1"/>
-      <sheetData sheetId="2949" refreshError="1"/>
-      <sheetData sheetId="2950" refreshError="1"/>
-      <sheetData sheetId="2951" refreshError="1"/>
-      <sheetData sheetId="2952" refreshError="1"/>
-      <sheetData sheetId="2953" refreshError="1"/>
-      <sheetData sheetId="2954" refreshError="1"/>
-      <sheetData sheetId="2955" refreshError="1"/>
-      <sheetData sheetId="2956" refreshError="1"/>
-      <sheetData sheetId="2957" refreshError="1"/>
-      <sheetData sheetId="2958" refreshError="1"/>
-      <sheetData sheetId="2959" refreshError="1"/>
-      <sheetData sheetId="2960" refreshError="1"/>
-      <sheetData sheetId="2961" refreshError="1"/>
-      <sheetData sheetId="2962" refreshError="1"/>
-      <sheetData sheetId="2963"/>
       <sheetData sheetId="2964"/>
-      <sheetData sheetId="2965"/>
-      <sheetData sheetId="2966"/>
-      <sheetData sheetId="2967"/>
-      <sheetData sheetId="2968"/>
-      <sheetData sheetId="2969"/>
-      <sheetData sheetId="2970"/>
-      <sheetData sheetId="2971"/>
-      <sheetData sheetId="2972"/>
-      <sheetData sheetId="2973"/>
+      <sheetData sheetId="2965" refreshError="1"/>
+      <sheetData sheetId="2966" refreshError="1"/>
+      <sheetData sheetId="2967" refreshError="1"/>
+      <sheetData sheetId="2968" refreshError="1"/>
+      <sheetData sheetId="2969" refreshError="1"/>
+      <sheetData sheetId="2970" refreshError="1"/>
+      <sheetData sheetId="2971" refreshError="1"/>
+      <sheetData sheetId="2972" refreshError="1"/>
+      <sheetData sheetId="2973" refreshError="1"/>
       <sheetData sheetId="2974" refreshError="1"/>
       <sheetData sheetId="2975"/>
       <sheetData sheetId="2976" refreshError="1"/>
@@ -19878,6 +20369,323 @@
       <sheetData sheetId="2982" refreshError="1"/>
       <sheetData sheetId="2983" refreshError="1"/>
       <sheetData sheetId="2984" refreshError="1"/>
+      <sheetData sheetId="2985" refreshError="1"/>
+      <sheetData sheetId="2986" refreshError="1"/>
+      <sheetData sheetId="2987" refreshError="1"/>
+      <sheetData sheetId="2988" refreshError="1"/>
+      <sheetData sheetId="2989" refreshError="1"/>
+      <sheetData sheetId="2990" refreshError="1"/>
+      <sheetData sheetId="2991" refreshError="1"/>
+      <sheetData sheetId="2992" refreshError="1"/>
+      <sheetData sheetId="2993" refreshError="1"/>
+      <sheetData sheetId="2994" refreshError="1"/>
+      <sheetData sheetId="2995" refreshError="1"/>
+      <sheetData sheetId="2996" refreshError="1"/>
+      <sheetData sheetId="2997" refreshError="1"/>
+      <sheetData sheetId="2998" refreshError="1"/>
+      <sheetData sheetId="2999" refreshError="1"/>
+      <sheetData sheetId="3000" refreshError="1"/>
+      <sheetData sheetId="3001" refreshError="1"/>
+      <sheetData sheetId="3002" refreshError="1"/>
+      <sheetData sheetId="3003" refreshError="1"/>
+      <sheetData sheetId="3004" refreshError="1"/>
+      <sheetData sheetId="3005" refreshError="1"/>
+      <sheetData sheetId="3006" refreshError="1"/>
+      <sheetData sheetId="3007" refreshError="1"/>
+      <sheetData sheetId="3008" refreshError="1"/>
+      <sheetData sheetId="3009" refreshError="1"/>
+      <sheetData sheetId="3010" refreshError="1"/>
+      <sheetData sheetId="3011" refreshError="1"/>
+      <sheetData sheetId="3012" refreshError="1"/>
+      <sheetData sheetId="3013" refreshError="1"/>
+      <sheetData sheetId="3014" refreshError="1"/>
+      <sheetData sheetId="3015" refreshError="1"/>
+      <sheetData sheetId="3016" refreshError="1"/>
+      <sheetData sheetId="3017" refreshError="1"/>
+      <sheetData sheetId="3018" refreshError="1"/>
+      <sheetData sheetId="3019" refreshError="1"/>
+      <sheetData sheetId="3020" refreshError="1"/>
+      <sheetData sheetId="3021" refreshError="1"/>
+      <sheetData sheetId="3022" refreshError="1"/>
+      <sheetData sheetId="3023" refreshError="1"/>
+      <sheetData sheetId="3024" refreshError="1"/>
+      <sheetData sheetId="3025" refreshError="1"/>
+      <sheetData sheetId="3026" refreshError="1"/>
+      <sheetData sheetId="3027" refreshError="1"/>
+      <sheetData sheetId="3028" refreshError="1"/>
+      <sheetData sheetId="3029" refreshError="1"/>
+      <sheetData sheetId="3030" refreshError="1"/>
+      <sheetData sheetId="3031" refreshError="1"/>
+      <sheetData sheetId="3032" refreshError="1"/>
+      <sheetData sheetId="3033" refreshError="1"/>
+      <sheetData sheetId="3034"/>
+      <sheetData sheetId="3035"/>
+      <sheetData sheetId="3036"/>
+      <sheetData sheetId="3037"/>
+      <sheetData sheetId="3038"/>
+      <sheetData sheetId="3039"/>
+      <sheetData sheetId="3040"/>
+      <sheetData sheetId="3041"/>
+      <sheetData sheetId="3042"/>
+      <sheetData sheetId="3043"/>
+      <sheetData sheetId="3044"/>
+      <sheetData sheetId="3045"/>
+      <sheetData sheetId="3046"/>
+      <sheetData sheetId="3047"/>
+      <sheetData sheetId="3048"/>
+      <sheetData sheetId="3049"/>
+      <sheetData sheetId="3050"/>
+      <sheetData sheetId="3051"/>
+      <sheetData sheetId="3052"/>
+      <sheetData sheetId="3053"/>
+      <sheetData sheetId="3054"/>
+      <sheetData sheetId="3055"/>
+      <sheetData sheetId="3056"/>
+      <sheetData sheetId="3057"/>
+      <sheetData sheetId="3058"/>
+      <sheetData sheetId="3059"/>
+      <sheetData sheetId="3060"/>
+      <sheetData sheetId="3061"/>
+      <sheetData sheetId="3062"/>
+      <sheetData sheetId="3063"/>
+      <sheetData sheetId="3064"/>
+      <sheetData sheetId="3065"/>
+      <sheetData sheetId="3066"/>
+      <sheetData sheetId="3067"/>
+      <sheetData sheetId="3068"/>
+      <sheetData sheetId="3069"/>
+      <sheetData sheetId="3070"/>
+      <sheetData sheetId="3071"/>
+      <sheetData sheetId="3072"/>
+      <sheetData sheetId="3073"/>
+      <sheetData sheetId="3074"/>
+      <sheetData sheetId="3075"/>
+      <sheetData sheetId="3076"/>
+      <sheetData sheetId="3077">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3078">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3079">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3080">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3081">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3082">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3083">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3084">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3085">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3086">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3087">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3088">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3089">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3090">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3091">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3092">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3093">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3094">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3095">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3096">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3097">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3098">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3099">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3100"/>
+      <sheetData sheetId="3101"/>
+      <sheetData sheetId="3102"/>
+      <sheetData sheetId="3103"/>
+      <sheetData sheetId="3104"/>
+      <sheetData sheetId="3105"/>
+      <sheetData sheetId="3106"/>
+      <sheetData sheetId="3107"/>
+      <sheetData sheetId="3108"/>
+      <sheetData sheetId="3109"/>
+      <sheetData sheetId="3110"/>
+      <sheetData sheetId="3111"/>
+      <sheetData sheetId="3112"/>
+      <sheetData sheetId="3113"/>
+      <sheetData sheetId="3114"/>
+      <sheetData sheetId="3115"/>
+      <sheetData sheetId="3116"/>
+      <sheetData sheetId="3117"/>
+      <sheetData sheetId="3118"/>
+      <sheetData sheetId="3119"/>
+      <sheetData sheetId="3120"/>
+      <sheetData sheetId="3121"/>
+      <sheetData sheetId="3122"/>
+      <sheetData sheetId="3123"/>
+      <sheetData sheetId="3124"/>
+      <sheetData sheetId="3125"/>
+      <sheetData sheetId="3126"/>
+      <sheetData sheetId="3127"/>
+      <sheetData sheetId="3128"/>
+      <sheetData sheetId="3129"/>
+      <sheetData sheetId="3130"/>
+      <sheetData sheetId="3131"/>
+      <sheetData sheetId="3132"/>
+      <sheetData sheetId="3133"/>
+      <sheetData sheetId="3134"/>
+      <sheetData sheetId="3135"/>
+      <sheetData sheetId="3136"/>
+      <sheetData sheetId="3137" refreshError="1"/>
+      <sheetData sheetId="3138" refreshError="1"/>
+      <sheetData sheetId="3139" refreshError="1"/>
+      <sheetData sheetId="3140" refreshError="1"/>
+      <sheetData sheetId="3141" refreshError="1"/>
+      <sheetData sheetId="3142" refreshError="1"/>
+      <sheetData sheetId="3143" refreshError="1"/>
+      <sheetData sheetId="3144" refreshError="1"/>
+      <sheetData sheetId="3145" refreshError="1"/>
+      <sheetData sheetId="3146" refreshError="1"/>
+      <sheetData sheetId="3147" refreshError="1"/>
+      <sheetData sheetId="3148" refreshError="1"/>
+      <sheetData sheetId="3149" refreshError="1"/>
+      <sheetData sheetId="3150" refreshError="1"/>
+      <sheetData sheetId="3151" refreshError="1"/>
+      <sheetData sheetId="3152" refreshError="1"/>
+      <sheetData sheetId="3153" refreshError="1"/>
+      <sheetData sheetId="3154" refreshError="1"/>
+      <sheetData sheetId="3155" refreshError="1"/>
+      <sheetData sheetId="3156" refreshError="1"/>
+      <sheetData sheetId="3157" refreshError="1"/>
+      <sheetData sheetId="3158" refreshError="1"/>
+      <sheetData sheetId="3159" refreshError="1"/>
+      <sheetData sheetId="3160" refreshError="1"/>
+      <sheetData sheetId="3161" refreshError="1"/>
+      <sheetData sheetId="3162" refreshError="1"/>
+      <sheetData sheetId="3163" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -19972,17 +20780,62 @@
       <sheetName val="_UnderConst_Analysis"/>
       <sheetName val="アップロード系(2)"/>
       <sheetName val="List"/>
+      <sheetName val="パラメータ設定表"/>
       <sheetName val="別紙7_操作系イベント発生時_"/>
       <sheetName val="別紙11_各競合条件における起動可否_"/>
       <sheetName val="index"/>
-      <sheetName val="パラメータ設定表"/>
+      <sheetName val="入力"/>
+      <sheetName val="415T戟L"/>
+      <sheetName val="No.31"/>
       <sheetName val="改訂履歴"/>
       <sheetName val="リスト"/>
       <sheetName val="ドメイン"/>
       <sheetName val="format"/>
-      <sheetName val="入力"/>
-      <sheetName val="415T戟L"/>
-      <sheetName val="No.31"/>
+      <sheetName val="Navigation"/>
+      <sheetName val="Cover"/>
+      <sheetName val="DataList"/>
+      <sheetName val="変更要件"/>
+      <sheetName val="【石倉編集中】DisplayStateTransitionTa"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="Data"/>
+      <sheetName val="★VarUsed"/>
+      <sheetName val="輝度計算(直線用)"/>
+      <sheetName val="コード_dimautocon"/>
+      <sheetName val="パラメータ_dimautocon"/>
+      <sheetName val="パラメータ_dimcalprcnt"/>
+      <sheetName val="パラメータ_dimmanualstep"/>
+      <sheetName val="パラメータ_dimmgr"/>
+      <sheetName val="XX-0080"/>
+      <sheetName val="メッセージ定義"/>
+      <sheetName val="XX-0180"/>
+      <sheetName val="lock"/>
+      <sheetName val="level"/>
+      <sheetName val="cominf"/>
+      <sheetName val="disconnect"/>
+      <sheetName val="９ｘ"/>
+      <sheetName val="Ｂｘ"/>
+      <sheetName val="Ｃｘ"/>
+      <sheetName val="Ｅｘ"/>
+      <sheetName val="休日"/>
+      <sheetName val="HMI-004_Screen（old）"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="MOTO"/>
+      <sheetName val="前提書情報"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="module"/>
+      <sheetName val="選択肢"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="メニュー"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="R0-10表紙MIC"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="修正ﾌｧｲﾙ一覧"/>
+      <sheetName val="RGB"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -20081,6 +20934,51 @@
       <sheetData sheetId="93" refreshError="1"/>
       <sheetData sheetId="94" refreshError="1"/>
       <sheetData sheetId="95" refreshError="1"/>
+      <sheetData sheetId="96" refreshError="1"/>
+      <sheetData sheetId="97" refreshError="1"/>
+      <sheetData sheetId="98" refreshError="1"/>
+      <sheetData sheetId="99" refreshError="1"/>
+      <sheetData sheetId="100" refreshError="1"/>
+      <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
+      <sheetData sheetId="133" refreshError="1"/>
+      <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -20377,10 +21275,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="52" width="2.125" style="241" customWidth="1"/>
-    <col min="53" max="16384" width="8.125" style="241"/>
+    <col min="1" max="52" width="2.08984375" style="241" customWidth="1"/>
+    <col min="53" max="16384" width="8.08984375" style="241"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -20438,32 +21336,32 @@
       <c r="AJ33" s="245"/>
     </row>
     <row r="34" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y34" s="244" t="s">
-        <v>322</v>
+      <c r="Y34" s="153" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y35" s="264" t="s">
-        <v>323</v>
-      </c>
-      <c r="Z35" s="265"/>
-      <c r="AA35" s="265"/>
-      <c r="AB35" s="265"/>
-      <c r="AC35" s="266"/>
-      <c r="AD35" s="264" t="s">
-        <v>324</v>
-      </c>
-      <c r="AE35" s="265"/>
-      <c r="AF35" s="265"/>
-      <c r="AG35" s="265"/>
-      <c r="AH35" s="266"/>
-      <c r="AI35" s="264" t="s">
-        <v>325</v>
-      </c>
-      <c r="AJ35" s="265"/>
-      <c r="AK35" s="265"/>
-      <c r="AL35" s="265"/>
-      <c r="AM35" s="266"/>
+      <c r="Y35" s="269" t="s">
+        <v>319</v>
+      </c>
+      <c r="Z35" s="270"/>
+      <c r="AA35" s="270"/>
+      <c r="AB35" s="270"/>
+      <c r="AC35" s="271"/>
+      <c r="AD35" s="269" t="s">
+        <v>320</v>
+      </c>
+      <c r="AE35" s="270"/>
+      <c r="AF35" s="270"/>
+      <c r="AG35" s="270"/>
+      <c r="AH35" s="271"/>
+      <c r="AI35" s="269" t="s">
+        <v>321</v>
+      </c>
+      <c r="AJ35" s="270"/>
+      <c r="AK35" s="270"/>
+      <c r="AL35" s="270"/>
+      <c r="AM35" s="271"/>
     </row>
     <row r="36" spans="3:39" ht="13.15" customHeight="1">
       <c r="D36" s="245"/>
@@ -20509,21 +21407,21 @@
       <c r="Y38" s="250"/>
       <c r="Z38" s="245"/>
       <c r="AA38" s="246" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AB38" s="245"/>
       <c r="AC38" s="252"/>
       <c r="AD38" s="250"/>
       <c r="AE38" s="245"/>
       <c r="AF38" s="246" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="AG38" s="245"/>
       <c r="AH38" s="252"/>
       <c r="AI38" s="253"/>
       <c r="AJ38" s="245"/>
       <c r="AK38" s="246" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AL38" s="245"/>
       <c r="AM38" s="252"/>
@@ -20558,31 +21456,31 @@
     <row r="41" spans="3:39" ht="13.15" customHeight="1"/>
     <row r="42" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y42" s="244" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y43" s="264" t="s">
-        <v>323</v>
-      </c>
-      <c r="Z43" s="265"/>
-      <c r="AA43" s="265"/>
-      <c r="AB43" s="265"/>
-      <c r="AC43" s="266"/>
-      <c r="AD43" s="264" t="s">
-        <v>324</v>
-      </c>
-      <c r="AE43" s="265"/>
-      <c r="AF43" s="265"/>
-      <c r="AG43" s="265"/>
-      <c r="AH43" s="266"/>
-      <c r="AI43" s="264" t="s">
-        <v>325</v>
-      </c>
-      <c r="AJ43" s="265"/>
-      <c r="AK43" s="265"/>
-      <c r="AL43" s="265"/>
-      <c r="AM43" s="266"/>
+      <c r="Y43" s="269" t="s">
+        <v>319</v>
+      </c>
+      <c r="Z43" s="270"/>
+      <c r="AA43" s="270"/>
+      <c r="AB43" s="270"/>
+      <c r="AC43" s="271"/>
+      <c r="AD43" s="269" t="s">
+        <v>320</v>
+      </c>
+      <c r="AE43" s="270"/>
+      <c r="AF43" s="270"/>
+      <c r="AG43" s="270"/>
+      <c r="AH43" s="271"/>
+      <c r="AI43" s="269" t="s">
+        <v>321</v>
+      </c>
+      <c r="AJ43" s="270"/>
+      <c r="AK43" s="270"/>
+      <c r="AL43" s="270"/>
+      <c r="AM43" s="271"/>
     </row>
     <row r="44" spans="3:39" ht="13.15" customHeight="1">
       <c r="D44" s="245"/>
@@ -20628,21 +21526,21 @@
       <c r="Y46" s="250"/>
       <c r="Z46" s="245"/>
       <c r="AA46" s="246" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="AB46" s="245"/>
       <c r="AC46" s="252"/>
       <c r="AD46" s="245"/>
       <c r="AE46" s="245"/>
       <c r="AF46" s="246" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="AG46" s="245"/>
       <c r="AH46" s="252"/>
       <c r="AI46" s="253"/>
       <c r="AJ46" s="245"/>
       <c r="AK46" s="246" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="AL46" s="245"/>
       <c r="AM46" s="252"/>
@@ -20676,31 +21574,31 @@
     <row r="49" spans="4:39" ht="13.15" customHeight="1"/>
     <row r="50" spans="4:39" ht="13.15" customHeight="1">
       <c r="Y50" s="244" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y51" s="264" t="s">
-        <v>323</v>
-      </c>
-      <c r="Z51" s="265"/>
-      <c r="AA51" s="265"/>
-      <c r="AB51" s="265"/>
-      <c r="AC51" s="266"/>
-      <c r="AD51" s="264" t="s">
-        <v>324</v>
-      </c>
-      <c r="AE51" s="265"/>
-      <c r="AF51" s="265"/>
-      <c r="AG51" s="265"/>
-      <c r="AH51" s="266"/>
-      <c r="AI51" s="264" t="s">
-        <v>325</v>
-      </c>
-      <c r="AJ51" s="265"/>
-      <c r="AK51" s="265"/>
-      <c r="AL51" s="265"/>
-      <c r="AM51" s="266"/>
+      <c r="Y51" s="269" t="s">
+        <v>319</v>
+      </c>
+      <c r="Z51" s="270"/>
+      <c r="AA51" s="270"/>
+      <c r="AB51" s="270"/>
+      <c r="AC51" s="271"/>
+      <c r="AD51" s="269" t="s">
+        <v>320</v>
+      </c>
+      <c r="AE51" s="270"/>
+      <c r="AF51" s="270"/>
+      <c r="AG51" s="270"/>
+      <c r="AH51" s="271"/>
+      <c r="AI51" s="269" t="s">
+        <v>321</v>
+      </c>
+      <c r="AJ51" s="270"/>
+      <c r="AK51" s="270"/>
+      <c r="AL51" s="270"/>
+      <c r="AM51" s="271"/>
     </row>
     <row r="52" spans="4:39" ht="13.15" customHeight="1">
       <c r="D52" s="245"/>
@@ -20746,21 +21644,21 @@
       <c r="Y54" s="250"/>
       <c r="Z54" s="245"/>
       <c r="AA54" s="246" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AB54" s="245"/>
       <c r="AC54" s="252"/>
       <c r="AD54" s="245"/>
       <c r="AE54" s="245"/>
       <c r="AF54" s="246" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AG54" s="245"/>
       <c r="AH54" s="252"/>
       <c r="AI54" s="253"/>
       <c r="AJ54" s="245"/>
       <c r="AK54" s="246" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AL54" s="245"/>
       <c r="AM54" s="252"/>
@@ -20791,7 +21689,7 @@
     </row>
     <row r="57" spans="4:39" ht="13.15" customHeight="1">
       <c r="AK57" s="241" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -20820,14 +21718,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="4.5" customWidth="1"/>
+    <col min="1" max="1" width="4.453125" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.5" customWidth="1"/>
-    <col min="5" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="22" width="13.125" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="13.125" customWidth="1"/>
+    <col min="4" max="4" width="69.453125" customWidth="1"/>
+    <col min="5" max="6" width="12.7265625" customWidth="1"/>
+    <col min="7" max="22" width="13.08984375" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -20838,18 +21736,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="280" t="s">
+      <c r="I2" s="272" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="280"/>
-      <c r="K2" s="280"/>
-      <c r="L2" s="280"/>
-      <c r="M2" s="280"/>
-      <c r="N2" s="280"/>
-      <c r="O2" s="280"/>
-      <c r="P2" s="280"/>
-      <c r="Q2" s="280"/>
-      <c r="R2" s="280"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="272"/>
+      <c r="L2" s="272"/>
+      <c r="M2" s="272"/>
+      <c r="N2" s="272"/>
+      <c r="O2" s="272"/>
+      <c r="P2" s="272"/>
+      <c r="Q2" s="272"/>
+      <c r="R2" s="272"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -20862,25 +21760,25 @@
       <c r="H3" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="I3" s="281" t="s">
+      <c r="I3" s="273" t="s">
         <v>203</v>
       </c>
-      <c r="J3" s="282"/>
-      <c r="K3" s="282"/>
-      <c r="L3" s="282"/>
-      <c r="M3" s="282"/>
-      <c r="N3" s="282"/>
-      <c r="O3" s="282"/>
-      <c r="P3" s="282"/>
-      <c r="Q3" s="282"/>
-      <c r="R3" s="282"/>
+      <c r="J3" s="274"/>
+      <c r="K3" s="274"/>
+      <c r="L3" s="274"/>
+      <c r="M3" s="274"/>
+      <c r="N3" s="274"/>
+      <c r="O3" s="274"/>
+      <c r="P3" s="274"/>
+      <c r="Q3" s="274"/>
+      <c r="R3" s="274"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="20" t="str">
         <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>1.0.1</v>
+        <v>1.0.2</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -20894,45 +21792,45 @@
       <c r="F5" s="6"/>
       <c r="H5" s="11">
         <f>MAX(B9:B14)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
+    <row r="7" spans="2:24">
+      <c r="C7" s="278" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="279"/>
+      <c r="E7" s="280" t="s">
         <v>2</v>
       </c>
+      <c r="F7" s="281"/>
+      <c r="G7" s="282" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="283"/>
+      <c r="I7" s="283"/>
+      <c r="J7" s="283"/>
+      <c r="K7" s="283"/>
+      <c r="L7" s="284"/>
+      <c r="M7" s="285" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="286"/>
+      <c r="O7" s="286"/>
+      <c r="P7" s="286"/>
+      <c r="Q7" s="286"/>
+      <c r="R7" s="287"/>
+      <c r="S7" s="275" t="s">
+        <v>333</v>
+      </c>
+      <c r="T7" s="276"/>
+      <c r="U7" s="276"/>
+      <c r="V7" s="276"/>
+      <c r="W7" s="276"/>
+      <c r="X7" s="277"/>
     </row>
-    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
-    <row r="7" spans="2:24">
-      <c r="C7" s="270" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="271"/>
-      <c r="E7" s="272" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="273"/>
-      <c r="G7" s="274" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="275"/>
-      <c r="I7" s="275"/>
-      <c r="J7" s="275"/>
-      <c r="K7" s="275"/>
-      <c r="L7" s="276"/>
-      <c r="M7" s="277" t="s">
-        <v>12</v>
-      </c>
-      <c r="N7" s="278"/>
-      <c r="O7" s="278"/>
-      <c r="P7" s="278"/>
-      <c r="Q7" s="278"/>
-      <c r="R7" s="279"/>
-      <c r="S7" s="267" t="s">
-        <v>337</v>
-      </c>
-      <c r="T7" s="268"/>
-      <c r="U7" s="268"/>
-      <c r="V7" s="268"/>
-      <c r="W7" s="268"/>
-      <c r="X7" s="269"/>
-    </row>
-    <row r="8" spans="2:24" ht="27.75" thickBot="1">
+    <row r="8" spans="2:24" ht="26.5" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>16</v>
       </c>
@@ -20985,7 +21883,7 @@
         <v>11</v>
       </c>
       <c r="S8" s="15" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="T8" s="15" t="s">
         <v>7</v>
@@ -21003,7 +21901,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="95.25" thickTop="1">
+    <row r="9" spans="2:24" ht="91.5" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -21012,7 +21910,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="261" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E9" s="262" t="s">
         <v>31</v>
@@ -21043,7 +21941,7 @@
       <c r="O9" s="262"/>
       <c r="P9" s="263"/>
       <c r="Q9" s="262" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="R9" s="263">
         <v>44375</v>
@@ -21067,16 +21965,16 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="40.5">
+    <row r="10" spans="2:24" ht="39">
       <c r="B10" s="9">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D10" s="237" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>31</v>
@@ -21113,21 +22011,29 @@
       <c r="U10" s="1"/>
       <c r="V10" s="239"/>
       <c r="W10" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="X10" s="238">
         <v>45807</v>
       </c>
     </row>
-    <row r="11" spans="2:24">
+    <row r="11" spans="2:24" ht="91">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="C11" s="264" t="s">
+        <v>339</v>
+      </c>
+      <c r="D11" s="265" t="s">
+        <v>341</v>
+      </c>
+      <c r="E11" s="266" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="266" t="s">
+        <v>31</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -21144,8 +22050,12 @@
       <c r="T11" s="239"/>
       <c r="U11" s="1"/>
       <c r="V11" s="239"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="238"/>
+      <c r="W11" s="267" t="s">
+        <v>340</v>
+      </c>
+      <c r="X11" s="268">
+        <v>46009</v>
+      </c>
     </row>
     <row r="12" spans="2:24">
       <c r="B12" s="9">
@@ -21175,7 +22085,7 @@
       <c r="W12" s="1"/>
       <c r="X12" s="238"/>
     </row>
-    <row r="13" spans="2:24" ht="14.25" thickBot="1">
+    <row r="13" spans="2:24" ht="13.5" thickBot="1">
       <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -21229,11 +22139,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="4.625" customWidth="1"/>
-    <col min="3" max="3" width="3.5" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="2" max="2" width="4.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.453125" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21247,13 +22157,13 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.25" thickBot="1">
+    <row r="6" spans="2:5" ht="13.5" thickBot="1">
       <c r="B6" s="153" t="s">
         <v>133</v>
       </c>
       <c r="C6" s="153"/>
     </row>
-    <row r="7" spans="2:5" ht="14.25" thickBot="1">
+    <row r="7" spans="2:5" ht="13.5" thickBot="1">
       <c r="C7" s="76" t="s">
         <v>135</v>
       </c>
@@ -21273,7 +22183,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="27">
+    <row r="9" spans="2:5" ht="26">
       <c r="C9" s="163">
         <v>1</v>
       </c>
@@ -21284,7 +22194,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="14.25" thickBot="1">
+    <row r="10" spans="2:5" ht="13.5" thickBot="1">
       <c r="C10" s="161"/>
       <c r="D10" s="87"/>
       <c r="E10" s="5"/>
@@ -21292,14 +22202,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="159"/>
     </row>
-    <row r="12" spans="2:5" ht="14.25" thickBot="1">
+    <row r="12" spans="2:5" ht="13.5" thickBot="1">
       <c r="B12" s="154" t="s">
         <v>134</v>
       </c>
       <c r="C12" s="83"/>
       <c r="D12" s="83"/>
     </row>
-    <row r="13" spans="2:5" ht="14.25" thickBot="1">
+    <row r="13" spans="2:5" ht="13.5" thickBot="1">
       <c r="B13" s="155"/>
       <c r="C13" s="160" t="s">
         <v>135</v>
@@ -21311,7 +22221,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="14.25" thickTop="1">
+    <row r="14" spans="2:5" ht="13.5" thickTop="1">
       <c r="C14" s="157">
         <v>0</v>
       </c>
@@ -21388,17 +22298,17 @@
         <v>171</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="14.25" thickBot="1">
+    <row r="21" spans="2:5" ht="13.5" thickBot="1">
       <c r="C21" s="161"/>
       <c r="D21" s="87"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="14.25" thickBot="1">
+    <row r="24" spans="2:5" ht="13.5" thickBot="1">
       <c r="B24" s="153" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="14.25" thickBot="1">
+    <row r="25" spans="2:5" ht="13.5" thickBot="1">
       <c r="C25" s="160" t="s">
         <v>135</v>
       </c>
@@ -21485,26 +22395,26 @@
       <c r="D33" s="86"/>
       <c r="E33" s="72"/>
     </row>
-    <row r="34" spans="2:5" ht="14.25" thickBot="1">
+    <row r="34" spans="2:5" ht="13.5" thickBot="1">
       <c r="C34" s="161"/>
       <c r="D34" s="87"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="14.25" thickBot="1">
+    <row r="37" spans="2:5" ht="13.5" thickBot="1">
       <c r="B37" s="153" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="283"/>
-      <c r="D38" s="284"/>
+      <c r="C38" s="288"/>
+      <c r="D38" s="289"/>
       <c r="E38" s="112" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="14.25" thickBot="1">
-      <c r="C39" s="285"/>
-      <c r="D39" s="286"/>
+    <row r="39" spans="2:5" ht="13.5" thickBot="1">
+      <c r="C39" s="290"/>
+      <c r="D39" s="291"/>
       <c r="E39" s="5" t="s">
         <v>121</v>
       </c>
@@ -21533,131 +22443,131 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.75" customWidth="1"/>
-    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.7265625" customWidth="1"/>
+    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="312" t="s">
+      <c r="B2" s="317" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="313"/>
-      <c r="D2" s="300" t="s">
-        <v>313</v>
-      </c>
-      <c r="E2" s="301"/>
-      <c r="F2" s="301"/>
-      <c r="G2" s="301"/>
-      <c r="H2" s="302"/>
+      <c r="C2" s="318"/>
+      <c r="D2" s="305" t="s">
+        <v>310</v>
+      </c>
+      <c r="E2" s="306"/>
+      <c r="F2" s="306"/>
+      <c r="G2" s="306"/>
+      <c r="H2" s="307"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="287" t="s">
+      <c r="B3" s="292" t="s">
         <v>117</v>
       </c>
-      <c r="C3" s="288"/>
-      <c r="D3" s="303" t="s">
-        <v>314</v>
-      </c>
-      <c r="E3" s="304"/>
-      <c r="F3" s="304"/>
-      <c r="G3" s="304"/>
-      <c r="H3" s="305"/>
+      <c r="C3" s="293"/>
+      <c r="D3" s="308" t="s">
+        <v>311</v>
+      </c>
+      <c r="E3" s="309"/>
+      <c r="F3" s="309"/>
+      <c r="G3" s="309"/>
+      <c r="H3" s="310"/>
     </row>
-    <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="298" t="s">
+    <row r="4" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B4" s="303" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="299"/>
-      <c r="D4" s="306" t="str">
+      <c r="C4" s="304"/>
+      <c r="D4" s="311" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_C_SLIP-CSTD-0-01-B-C0.c</v>
       </c>
-      <c r="E4" s="307"/>
-      <c r="F4" s="307"/>
-      <c r="G4" s="307"/>
-      <c r="H4" s="308"/>
+      <c r="E4" s="312"/>
+      <c r="F4" s="312"/>
+      <c r="G4" s="312"/>
+      <c r="H4" s="313"/>
     </row>
-    <row r="5" spans="2:14" ht="14.25" thickBot="1">
+    <row r="5" spans="2:14" ht="13.5" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="312" t="s">
+      <c r="B6" s="317" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="313"/>
-      <c r="D6" s="309" t="str">
+      <c r="C6" s="318"/>
+      <c r="D6" s="314" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>C_SLIP</v>
       </c>
-      <c r="E6" s="310"/>
-      <c r="F6" s="310"/>
-      <c r="G6" s="310"/>
-      <c r="H6" s="311"/>
+      <c r="E6" s="315"/>
+      <c r="F6" s="315"/>
+      <c r="G6" s="315"/>
+      <c r="H6" s="316"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="287" t="s">
+      <c r="B7" s="292" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="288"/>
-      <c r="D7" s="289">
+      <c r="C7" s="293"/>
+      <c r="D7" s="294">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="290"/>
-      <c r="F7" s="290"/>
-      <c r="G7" s="290"/>
-      <c r="H7" s="291"/>
+      <c r="E7" s="295"/>
+      <c r="F7" s="295"/>
+      <c r="G7" s="295"/>
+      <c r="H7" s="296"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="287" t="s">
+      <c r="B8" s="292" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="288"/>
-      <c r="D8" s="289" t="str">
+      <c r="C8" s="293"/>
+      <c r="D8" s="294" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_C_SLIP_MTRX</v>
       </c>
-      <c r="E8" s="290"/>
-      <c r="F8" s="290"/>
-      <c r="G8" s="290"/>
-      <c r="H8" s="291"/>
+      <c r="E8" s="295"/>
+      <c r="F8" s="295"/>
+      <c r="G8" s="295"/>
+      <c r="H8" s="296"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="287" t="s">
+      <c r="B9" s="292" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="288"/>
-      <c r="D9" s="292" t="s">
-        <v>312</v>
-      </c>
-      <c r="E9" s="293"/>
-      <c r="F9" s="293"/>
-      <c r="G9" s="293"/>
-      <c r="H9" s="294"/>
+      <c r="C9" s="293"/>
+      <c r="D9" s="297" t="s">
+        <v>309</v>
+      </c>
+      <c r="E9" s="298"/>
+      <c r="F9" s="298"/>
+      <c r="G9" s="298"/>
+      <c r="H9" s="299"/>
     </row>
-    <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="298" t="s">
+    <row r="10" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B10" s="303" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="299"/>
-      <c r="D10" s="295"/>
-      <c r="E10" s="296"/>
-      <c r="F10" s="296"/>
-      <c r="G10" s="296"/>
-      <c r="H10" s="297"/>
+      <c r="C10" s="304"/>
+      <c r="D10" s="300"/>
+      <c r="E10" s="301"/>
+      <c r="F10" s="301"/>
+      <c r="G10" s="301"/>
+      <c r="H10" s="302"/>
     </row>
-    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
-    <row r="12" spans="2:14" ht="14.25" thickBot="1">
+    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.5" thickBot="1">
       <c r="B12" s="144" t="s">
         <v>34</v>
       </c>
@@ -21692,7 +22602,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="14.25" thickTop="1">
+    <row r="13" spans="2:14" ht="13.5" thickTop="1">
       <c r="B13" s="105">
         <v>1</v>
       </c>
@@ -21703,15 +22613,15 @@
         <v>48</v>
       </c>
       <c r="E13" s="111" t="s">
-        <v>269</v>
+        <v>342</v>
       </c>
       <c r="F13" s="50" t="str">
         <f t="shared" ref="F13:F37" ca="1" si="0">IF($D13&lt;&gt;"","u4_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"Srcchk","")</f>
         <v>u4_s_AlertC_slipSrcchk</v>
       </c>
       <c r="G13" s="50" t="str">
-        <f t="shared" ref="G13:G37" ca="1" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
-        <v>vd_s_AlertC_slipRwTx</v>
+        <f t="shared" ref="G13:G37" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
+        <v>NULL</v>
       </c>
       <c r="H13" s="109" t="str">
         <f ca="1">IF($D13&lt;&gt;"","ALERT_CH_"&amp;UPPER($D$6)&amp;IF($D$7=1,"","_"&amp;UPPER($C13)),"")</f>
@@ -22545,7 +23455,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="14.25" thickBot="1">
+    <row r="37" spans="2:14" ht="13.5" thickBot="1">
       <c r="B37" s="96">
         <v>25</v>
       </c>
@@ -22644,21 +23554,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.5" customWidth="1"/>
-    <col min="6" max="6" width="52.75" customWidth="1"/>
-    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.875" customWidth="1"/>
-    <col min="16" max="16" width="9.875" customWidth="1"/>
-    <col min="17" max="17" width="44.625" customWidth="1"/>
-    <col min="18" max="18" width="73.625" customWidth="1"/>
+    <col min="5" max="5" width="36.453125" customWidth="1"/>
+    <col min="6" max="6" width="52.7265625" customWidth="1"/>
+    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.90625" customWidth="1"/>
+    <col min="16" max="16" width="9.90625" customWidth="1"/>
+    <col min="17" max="17" width="44.6328125" customWidth="1"/>
+    <col min="18" max="18" width="73.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="14.25" thickBot="1">
+    <row r="2" spans="2:18" ht="13.5" thickBot="1">
       <c r="B2" t="s">
         <v>193</v>
       </c>
@@ -22666,7 +23576,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="14.25" thickBot="1">
+    <row r="3" spans="2:18" ht="13.5" thickBot="1">
       <c r="B3" s="144" t="s">
         <v>34</v>
       </c>
@@ -22704,7 +23614,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B4" s="175">
         <v>0</v>
       </c>
@@ -22732,12 +23642,12 @@
       </c>
       <c r="R4" s="142"/>
     </row>
-    <row r="5" spans="2:18" ht="27.75" thickTop="1">
+    <row r="5" spans="2:18" ht="26.5" thickTop="1">
       <c r="B5" s="178">
         <v>1</v>
       </c>
       <c r="C5" s="206" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D5" s="107" t="s">
         <v>267</v>
@@ -22747,7 +23657,7 @@
         <v>ALERT_OPT_ID_C_SLIP_VSCEXIST</v>
       </c>
       <c r="F5" s="236" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G5" s="66">
         <f ca="1">IF(E5&lt;&gt;"",LEN(E5),"")</f>
@@ -23266,7 +24176,7 @@
       <c r="Q28" s="148"/>
       <c r="R28" s="117"/>
     </row>
-    <row r="29" spans="2:18" ht="14.25" thickBot="1">
+    <row r="29" spans="2:18" ht="13.5" thickBot="1">
       <c r="B29" s="179">
         <v>25</v>
       </c>
@@ -23288,7 +24198,7 @@
       <c r="Q29" s="146"/>
       <c r="R29" s="119"/>
     </row>
-    <row r="32" spans="2:18" ht="14.25" thickBot="1">
+    <row r="32" spans="2:18" ht="13.5" thickBot="1">
       <c r="B32" t="s">
         <v>194</v>
       </c>
@@ -23296,7 +24206,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="14.25" thickBot="1">
+    <row r="33" spans="2:18" ht="13.5" thickBot="1">
       <c r="B33" s="144" t="s">
         <v>34</v>
       </c>
@@ -23328,7 +24238,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B34" s="175">
         <v>0</v>
       </c>
@@ -23354,7 +24264,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="14.25" thickTop="1">
+    <row r="35" spans="2:18" ht="13.5" thickTop="1">
       <c r="B35" s="178">
         <v>1</v>
       </c>
@@ -23882,7 +24792,7 @@
       <c r="Q58" s="148"/>
       <c r="R58" s="180"/>
     </row>
-    <row r="59" spans="2:18" ht="14.25" thickBot="1">
+    <row r="59" spans="2:18" ht="13.5" thickBot="1">
       <c r="B59" s="179">
         <v>25</v>
       </c>
@@ -23933,27 +24843,27 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="28.375" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="5" max="5" width="12.375" customWidth="1"/>
-    <col min="6" max="6" width="19.75" customWidth="1"/>
-    <col min="7" max="7" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" customWidth="1"/>
+    <col min="6" max="6" width="19.7265625" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="11" width="12.375" customWidth="1"/>
-    <col min="12" max="12" width="16.125" customWidth="1"/>
-    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
+    <col min="9" max="11" width="12.36328125" customWidth="1"/>
+    <col min="12" max="12" width="16.08984375" customWidth="1"/>
+    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.25" thickBot="1">
+    <row r="1" spans="2:21" ht="13.5" thickBot="1">
       <c r="C1" s="89" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="14.25" thickBot="1">
+    <row r="2" spans="2:21" ht="13.5" thickBot="1">
       <c r="B2" s="97" t="s">
         <v>58</v>
       </c>
@@ -23997,7 +24907,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="22"/>
       <c r="C3" s="49" t="s">
         <v>106</v>
@@ -24018,7 +24928,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="14.25" thickTop="1">
+    <row r="4" spans="2:21" ht="13.5" thickTop="1">
       <c r="B4" s="22" t="s">
         <v>261</v>
       </c>
@@ -24123,13 +25033,13 @@
         <v>261</v>
       </c>
       <c r="C6" s="106" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D6" s="120">
         <v>2</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F6" s="205" t="s">
         <v>266</v>
@@ -24173,13 +25083,13 @@
         <v>261</v>
       </c>
       <c r="C7" s="213" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D7" s="224">
         <v>3</v>
       </c>
       <c r="E7" s="223" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F7" s="215" t="s">
         <v>266</v>
@@ -24197,10 +25107,10 @@
         <v>129</v>
       </c>
       <c r="K7" s="223" t="s">
-        <v>303</v>
+        <v>128</v>
       </c>
       <c r="L7" s="215" t="s">
-        <v>268</v>
+        <v>129</v>
       </c>
       <c r="M7" s="45">
         <f t="shared" ca="1" si="1"/>
@@ -24352,7 +25262,7 @@
       </c>
       <c r="U12" s="30"/>
     </row>
-    <row r="13" spans="2:21" ht="14.25" thickBot="1">
+    <row r="13" spans="2:21" ht="13.5" thickBot="1">
       <c r="B13" s="22"/>
       <c r="C13" s="21"/>
       <c r="D13" s="116"/>
@@ -26603,7 +27513,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="14.25" thickBot="1">
+    <row r="103" spans="2:15" ht="13.5" thickBot="1">
       <c r="B103" s="51"/>
       <c r="C103" s="52"/>
       <c r="D103" s="118"/>
@@ -26676,18 +27586,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.125" customWidth="1"/>
+    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.08984375" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.125" customWidth="1"/>
-    <col min="48" max="48" width="23.625" customWidth="1"/>
+    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.08984375" customWidth="1"/>
+    <col min="48" max="48" width="23.6328125" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26703,7 +27613,7 @@
       <c r="B2" s="126" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="314" t="s">
+      <c r="C2" s="319" t="s">
         <v>81</v>
       </c>
       <c r="D2" s="56">
@@ -26802,7 +27712,7 @@
       <c r="AI2" s="56">
         <v>0</v>
       </c>
-      <c r="AJ2" s="316" t="s">
+      <c r="AJ2" s="321" t="s">
         <v>159</v>
       </c>
     </row>
@@ -26811,7 +27721,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="315"/>
+      <c r="C3" s="320"/>
       <c r="D3" s="128" t="s">
         <v>61</v>
       </c>
@@ -26891,27 +27801,27 @@
         <v>66</v>
       </c>
       <c r="AD3" s="203" t="s">
-        <v>321</v>
-      </c>
-      <c r="AE3" s="322" t="s">
+        <v>318</v>
+      </c>
+      <c r="AE3" s="327" t="s">
         <v>204</v>
       </c>
-      <c r="AF3" s="323"/>
-      <c r="AG3" s="322" t="s">
-        <v>320</v>
-      </c>
-      <c r="AH3" s="324"/>
-      <c r="AI3" s="323"/>
-      <c r="AJ3" s="317"/>
+      <c r="AF3" s="328"/>
+      <c r="AG3" s="327" t="s">
+        <v>317</v>
+      </c>
+      <c r="AH3" s="329"/>
+      <c r="AI3" s="328"/>
+      <c r="AJ3" s="322"/>
       <c r="AR3" s="90" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A4" s="318" t="s">
+    <row r="4" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A4" s="323" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="319"/>
+      <c r="B4" s="324"/>
       <c r="C4" s="138"/>
       <c r="D4" s="138"/>
       <c r="E4" s="138"/>
@@ -26955,9 +27865,9 @@
       <c r="AV4" s="79"/>
       <c r="AW4" s="80"/>
     </row>
-    <row r="5" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A5" s="320"/>
-      <c r="B5" s="321"/>
+    <row r="5" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A5" s="325"/>
+      <c r="B5" s="326"/>
       <c r="C5" s="139"/>
       <c r="D5" s="139"/>
       <c r="E5" s="139"/>
@@ -27139,7 +28049,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_UNKNOWN,                                                     /* 00 UNKNOWN                                         */</v>
       </c>
       <c r="AU6" s="61" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AV6" s="46" t="s">
         <v>68</v>
@@ -27385,7 +28295,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="21" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AL8" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27405,7 +28315,7 @@
       </c>
       <c r="AU8" s="61" t="str">
         <f ca="1">IF($AW$15&lt;&gt;"NULL","        &amp;"&amp;$AW$15&amp;","&amp;REPT(" ",69-LEN($AW$15))&amp;"/* fp_vd_XDST                                         */","        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */")</f>
-        <v xml:space="preserve">        &amp;vd_s_AlertC_slipRwTx,                                                 /* fp_vd_XDST                                         */</v>
+        <v xml:space="preserve">        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */</v>
       </c>
       <c r="AV8" s="47" t="s">
         <v>70</v>
@@ -27648,7 +28558,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="21" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AL10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -28044,7 +28954,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" s="21" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AL13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -28337,7 +29247,7 @@
       </c>
       <c r="AW15" s="66" t="str">
         <f ca="1">IF(AW6&lt;&gt;AW17,VLOOKUP(AW6,Matrix!$C$13:$G$37,5,FALSE),Matrix!G13)</f>
-        <v>vd_s_AlertC_slipRwTx</v>
+        <v>NULL</v>
       </c>
     </row>
     <row r="16" spans="1:49">
@@ -28462,7 +29372,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_UNKNOWN,                                                     /* 10 UNKNOWN                                         */</v>
       </c>
       <c r="AU16" s="61" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AV16" s="47" t="s">
         <v>76</v>
@@ -28472,7 +29382,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="14.25" thickBot="1">
+    <row r="17" spans="2:49" ht="13.5" thickBot="1">
       <c r="B17" s="135"/>
       <c r="C17" s="45">
         <f t="shared" si="2"/>
@@ -28594,7 +29504,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_UNKNOWN,                                                     /* 11 UNKNOWN                                         */</v>
       </c>
       <c r="AU17" s="62" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AV17" s="48" t="s">
         <v>77</v>
@@ -29195,7 +30105,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL22" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29317,7 +30227,7 @@
         <v>1</v>
       </c>
       <c r="AJ23" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL23" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29439,7 +30349,7 @@
         <v>0</v>
       </c>
       <c r="AJ24" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL24" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29561,7 +30471,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29683,7 +30593,7 @@
         <v>0</v>
       </c>
       <c r="AJ26" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL26" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29805,7 +30715,7 @@
         <v>1</v>
       </c>
       <c r="AJ27" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL27" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29927,7 +30837,7 @@
         <v>0</v>
       </c>
       <c r="AJ28" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL28" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30049,7 +30959,7 @@
         <v>1</v>
       </c>
       <c r="AJ29" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL29" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30171,7 +31081,7 @@
         <v>0</v>
       </c>
       <c r="AJ30" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL30" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30293,7 +31203,7 @@
         <v>1</v>
       </c>
       <c r="AJ31" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL31" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30415,7 +31325,7 @@
         <v>0</v>
       </c>
       <c r="AJ32" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL32" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30537,7 +31447,7 @@
         <v>1</v>
       </c>
       <c r="AJ33" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL33" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30659,7 +31569,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL34" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30781,7 +31691,7 @@
         <v>1</v>
       </c>
       <c r="AJ35" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL35" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30903,7 +31813,7 @@
         <v>0</v>
       </c>
       <c r="AJ36" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL36" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -31025,7 +31935,7 @@
         <v>1</v>
       </c>
       <c r="AJ37" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL37" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -31391,7 +32301,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" s="21" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AL40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -31635,7 +32545,7 @@
         <v>0</v>
       </c>
       <c r="AJ42" s="21" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AL42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -32001,7 +32911,7 @@
         <v>1</v>
       </c>
       <c r="AJ45" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL45" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33099,7 +34009,7 @@
         <v>0</v>
       </c>
       <c r="AJ54" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL54" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33221,7 +34131,7 @@
         <v>1</v>
       </c>
       <c r="AJ55" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL55" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33343,7 +34253,7 @@
         <v>0</v>
       </c>
       <c r="AJ56" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL56" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33465,7 +34375,7 @@
         <v>1</v>
       </c>
       <c r="AJ57" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL57" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33587,7 +34497,7 @@
         <v>0</v>
       </c>
       <c r="AJ58" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL58" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33709,7 +34619,7 @@
         <v>1</v>
       </c>
       <c r="AJ59" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL59" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33831,7 +34741,7 @@
         <v>0</v>
       </c>
       <c r="AJ60" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL60" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33953,7 +34863,7 @@
         <v>1</v>
       </c>
       <c r="AJ61" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL61" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34075,7 +34985,7 @@
         <v>0</v>
       </c>
       <c r="AJ62" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL62" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34197,7 +35107,7 @@
         <v>1</v>
       </c>
       <c r="AJ63" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL63" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34319,7 +35229,7 @@
         <v>0</v>
       </c>
       <c r="AJ64" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL64" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34441,7 +35351,7 @@
         <v>1</v>
       </c>
       <c r="AJ65" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL65" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34563,7 +35473,7 @@
         <v>0</v>
       </c>
       <c r="AJ66" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL66" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34685,7 +35595,7 @@
         <v>1</v>
       </c>
       <c r="AJ67" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL67" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34807,7 +35717,7 @@
         <v>0</v>
       </c>
       <c r="AJ68" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL68" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34929,7 +35839,7 @@
         <v>1</v>
       </c>
       <c r="AJ69" s="218" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AL69" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34948,7 +35858,7 @@
         <v xml:space="preserve">    (U1)ALERT_REQ_C_SLIP_MALFUNC_RW                                            /* 63 MALFUNC_RW                                      */</v>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="14.25" thickBot="1">
+    <row r="70" spans="1:46" ht="13.5" thickBot="1">
       <c r="A70" s="54" t="s">
         <v>64</v>
       </c>
@@ -55610,19 +56520,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:AS91"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="41" customWidth="1"/>
-    <col min="3" max="10" width="3.375" customWidth="1"/>
+    <col min="3" max="10" width="3.36328125" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="20.875" customWidth="1"/>
+    <col min="12" max="12" width="20.90625" customWidth="1"/>
     <col min="13" max="13" width="19" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="10.875" customWidth="1"/>
-    <col min="18" max="18" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="10.90625" customWidth="1"/>
+    <col min="18" max="18" width="14.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:45" ht="15" thickBot="1">
+    <row r="2" spans="2:45" ht="14.5" thickBot="1">
       <c r="B2" s="23" t="s">
         <v>207</v>
       </c>
@@ -55654,20 +56564,20 @@
       <c r="AR2" s="202"/>
       <c r="AS2" s="202"/>
     </row>
-    <row r="3" spans="2:45" ht="15" thickBot="1">
+    <row r="3" spans="2:45" ht="14.5" thickBot="1">
       <c r="B3" s="94" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="329" t="s">
-        <v>298</v>
-      </c>
-      <c r="D3" s="330"/>
-      <c r="E3" s="330"/>
-      <c r="F3" s="330"/>
-      <c r="G3" s="330"/>
-      <c r="H3" s="330"/>
-      <c r="I3" s="330"/>
-      <c r="J3" s="331"/>
+      <c r="C3" s="334" t="s">
+        <v>296</v>
+      </c>
+      <c r="D3" s="335"/>
+      <c r="E3" s="335"/>
+      <c r="F3" s="335"/>
+      <c r="G3" s="335"/>
+      <c r="H3" s="335"/>
+      <c r="I3" s="335"/>
+      <c r="J3" s="336"/>
       <c r="K3" s="171"/>
       <c r="L3" s="171"/>
       <c r="M3" s="171"/>
@@ -55706,16 +56616,16 @@
       <c r="B5" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="325" t="s">
+      <c r="C5" s="330" t="s">
         <v>211</v>
       </c>
-      <c r="D5" s="326"/>
-      <c r="E5" s="326"/>
-      <c r="F5" s="326"/>
-      <c r="G5" s="326"/>
-      <c r="H5" s="326"/>
-      <c r="I5" s="326"/>
-      <c r="J5" s="327"/>
+      <c r="D5" s="331"/>
+      <c r="E5" s="331"/>
+      <c r="F5" s="331"/>
+      <c r="G5" s="331"/>
+      <c r="H5" s="331"/>
+      <c r="I5" s="331"/>
+      <c r="J5" s="332"/>
       <c r="K5" s="193" t="s">
         <v>23</v>
       </c>
@@ -55741,7 +56651,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:45" ht="40.5">
+    <row r="6" spans="2:45" ht="39">
       <c r="B6" s="69" t="s">
         <v>33</v>
       </c>
@@ -55785,23 +56695,23 @@
       <c r="P6" s="75"/>
       <c r="Q6" s="75"/>
       <c r="R6" s="88" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
-    <row r="7" spans="2:45" ht="27">
+    <row r="7" spans="2:45" ht="26">
       <c r="B7" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="328" t="s">
+      <c r="C7" s="333" t="s">
         <v>219</v>
       </c>
-      <c r="D7" s="326"/>
-      <c r="E7" s="326"/>
-      <c r="F7" s="326"/>
-      <c r="G7" s="326"/>
-      <c r="H7" s="326"/>
-      <c r="I7" s="326"/>
-      <c r="J7" s="327"/>
+      <c r="D7" s="331"/>
+      <c r="E7" s="331"/>
+      <c r="F7" s="331"/>
+      <c r="G7" s="331"/>
+      <c r="H7" s="331"/>
+      <c r="I7" s="331"/>
+      <c r="J7" s="332"/>
       <c r="K7" s="1" t="s">
         <v>220</v>
       </c>
@@ -55816,10 +56726,10 @@
       <c r="P7" s="75"/>
       <c r="Q7" s="75"/>
       <c r="R7" s="72" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
-    <row r="8" spans="2:45" ht="136.5">
+    <row r="8" spans="2:45" ht="131">
       <c r="B8" s="69" t="s">
         <v>29</v>
       </c>
@@ -55848,13 +56758,13 @@
         <v>228</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="L8" s="25" t="s">
         <v>229</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="N8" s="30" t="s">
         <v>230</v>
@@ -55866,7 +56776,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="9" spans="2:45" ht="68.25" thickBot="1">
+    <row r="9" spans="2:45" ht="65.5" thickBot="1">
       <c r="B9" s="71" t="s">
         <v>30</v>
       </c>
@@ -55915,9 +56825,9 @@
         <v>239</v>
       </c>
     </row>
-    <row r="10" spans="2:45" ht="14.25" thickTop="1">
+    <row r="10" spans="2:45" ht="13.5" thickTop="1">
       <c r="B10" s="209" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C10" s="169"/>
       <c r="D10" s="169"/>
@@ -55928,10 +56838,10 @@
       <c r="I10" s="169"/>
       <c r="J10" s="169"/>
       <c r="K10" s="197" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L10" s="36" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M10" s="192" t="s">
         <v>253</v>
@@ -55950,7 +56860,7 @@
     </row>
     <row r="11" spans="2:45">
       <c r="B11" s="209" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C11" s="170"/>
       <c r="D11" s="170"/>
@@ -55961,10 +56871,10 @@
       <c r="I11" s="170"/>
       <c r="J11" s="170"/>
       <c r="K11" s="200" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L11" s="36" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M11" s="192" t="s">
         <v>254</v>
@@ -55983,7 +56893,7 @@
     </row>
     <row r="12" spans="2:45">
       <c r="B12" s="209" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C12" s="170"/>
       <c r="D12" s="170"/>
@@ -55994,10 +56904,10 @@
       <c r="I12" s="170"/>
       <c r="J12" s="170"/>
       <c r="K12" s="200" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L12" s="36" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M12" s="192" t="s">
         <v>241</v>
@@ -56016,7 +56926,7 @@
     </row>
     <row r="13" spans="2:45">
       <c r="B13" s="209" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C13" s="170"/>
       <c r="D13" s="170"/>
@@ -56027,10 +56937,10 @@
       <c r="I13" s="170"/>
       <c r="J13" s="170"/>
       <c r="K13" s="200" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L13" s="36" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M13" s="192" t="s">
         <v>255</v>
@@ -56049,7 +56959,7 @@
     </row>
     <row r="14" spans="2:45">
       <c r="B14" s="209" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C14" s="170"/>
       <c r="D14" s="170"/>
@@ -56060,10 +56970,10 @@
       <c r="I14" s="170"/>
       <c r="J14" s="170"/>
       <c r="K14" s="200" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L14" s="36" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M14" s="192" t="s">
         <v>256</v>
@@ -56082,7 +56992,7 @@
     </row>
     <row r="15" spans="2:45">
       <c r="B15" s="209" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C15" s="170"/>
       <c r="D15" s="170"/>
@@ -56093,10 +57003,10 @@
       <c r="I15" s="170"/>
       <c r="J15" s="170"/>
       <c r="K15" s="200" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M15" s="192" t="s">
         <v>247</v>
@@ -56115,7 +57025,7 @@
     </row>
     <row r="16" spans="2:45">
       <c r="B16" s="209" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C16" s="170"/>
       <c r="D16" s="170"/>
@@ -56126,10 +57036,10 @@
       <c r="I16" s="170"/>
       <c r="J16" s="170"/>
       <c r="K16" s="200" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L16" s="36" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M16" s="192" t="s">
         <v>248</v>
@@ -56148,7 +57058,7 @@
     </row>
     <row r="17" spans="2:18">
       <c r="B17" s="209" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C17" s="170"/>
       <c r="D17" s="170"/>
@@ -56159,16 +57069,16 @@
       <c r="I17" s="170"/>
       <c r="J17" s="170"/>
       <c r="K17" s="207" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L17" s="36" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M17" s="192" t="s">
         <v>249</v>
       </c>
       <c r="N17" s="235" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="O17" s="37" t="s">
         <v>206</v>
@@ -56181,7 +57091,7 @@
     </row>
     <row r="18" spans="2:18">
       <c r="B18" s="209" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C18" s="169"/>
       <c r="D18" s="169"/>
@@ -56192,10 +57102,10 @@
       <c r="I18" s="169"/>
       <c r="J18" s="169"/>
       <c r="K18" s="200" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L18" s="210" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M18" s="192" t="s">
         <v>253</v>
@@ -56214,7 +57124,7 @@
     </row>
     <row r="19" spans="2:18">
       <c r="B19" s="209" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C19" s="170"/>
       <c r="D19" s="170"/>
@@ -56225,10 +57135,10 @@
       <c r="I19" s="170"/>
       <c r="J19" s="170"/>
       <c r="K19" s="216" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L19" s="210" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M19" s="192" t="s">
         <v>254</v>
@@ -56247,7 +57157,7 @@
     </row>
     <row r="20" spans="2:18">
       <c r="B20" s="209" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C20" s="170"/>
       <c r="D20" s="170"/>
@@ -56258,10 +57168,10 @@
       <c r="I20" s="170"/>
       <c r="J20" s="170"/>
       <c r="K20" s="216" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L20" s="210" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M20" s="192" t="s">
         <v>241</v>
@@ -56280,7 +57190,7 @@
     </row>
     <row r="21" spans="2:18">
       <c r="B21" s="209" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C21" s="170"/>
       <c r="D21" s="170"/>
@@ -56291,10 +57201,10 @@
       <c r="I21" s="170"/>
       <c r="J21" s="170"/>
       <c r="K21" s="216" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L21" s="210" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M21" s="192" t="s">
         <v>255</v>
@@ -56313,7 +57223,7 @@
     </row>
     <row r="22" spans="2:18">
       <c r="B22" s="209" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C22" s="170"/>
       <c r="D22" s="170"/>
@@ -56324,10 +57234,10 @@
       <c r="I22" s="170"/>
       <c r="J22" s="170"/>
       <c r="K22" s="216" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L22" s="210" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M22" s="192" t="s">
         <v>256</v>
@@ -56346,7 +57256,7 @@
     </row>
     <row r="23" spans="2:18">
       <c r="B23" s="209" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C23" s="170"/>
       <c r="D23" s="170"/>
@@ -56357,10 +57267,10 @@
       <c r="I23" s="170"/>
       <c r="J23" s="170"/>
       <c r="K23" s="216" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L23" s="210" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M23" s="192" t="s">
         <v>247</v>
@@ -56379,7 +57289,7 @@
     </row>
     <row r="24" spans="2:18">
       <c r="B24" s="209" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C24" s="170"/>
       <c r="D24" s="170"/>
@@ -56390,10 +57300,10 @@
       <c r="I24" s="170"/>
       <c r="J24" s="170"/>
       <c r="K24" s="216" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L24" s="210" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M24" s="192" t="s">
         <v>248</v>
@@ -56412,7 +57322,7 @@
     </row>
     <row r="25" spans="2:18">
       <c r="B25" s="209" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C25" s="170"/>
       <c r="D25" s="170"/>
@@ -56423,10 +57333,10 @@
       <c r="I25" s="170"/>
       <c r="J25" s="170"/>
       <c r="K25" s="216" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="L25" s="210" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M25" s="192" t="s">
         <v>249</v>
@@ -56445,7 +57355,7 @@
     </row>
     <row r="26" spans="2:18">
       <c r="B26" s="209" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C26" s="169"/>
       <c r="D26" s="169"/>
@@ -56456,13 +57366,13 @@
       <c r="I26" s="169"/>
       <c r="J26" s="169"/>
       <c r="K26" s="200" t="s">
+        <v>284</v>
+      </c>
+      <c r="L26" s="36" t="s">
+        <v>271</v>
+      </c>
+      <c r="M26" s="192" t="s">
         <v>286</v>
-      </c>
-      <c r="L26" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="M26" s="192" t="s">
-        <v>288</v>
       </c>
       <c r="N26" s="212" t="s">
         <v>32</v>
@@ -56478,7 +57388,7 @@
     </row>
     <row r="27" spans="2:18">
       <c r="B27" s="209" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C27" s="170"/>
       <c r="D27" s="170"/>
@@ -56489,13 +57399,13 @@
       <c r="I27" s="170"/>
       <c r="J27" s="170"/>
       <c r="K27" s="216" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L27" s="36" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="M27" s="192" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="N27" s="212" t="s">
         <v>250</v>
@@ -56511,7 +57421,7 @@
     </row>
     <row r="28" spans="2:18">
       <c r="B28" s="209" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C28" s="170"/>
       <c r="D28" s="170"/>
@@ -56522,13 +57432,13 @@
       <c r="I28" s="170"/>
       <c r="J28" s="170"/>
       <c r="K28" s="216" t="s">
+        <v>284</v>
+      </c>
+      <c r="L28" s="36" t="s">
+        <v>285</v>
+      </c>
+      <c r="M28" s="192" t="s">
         <v>286</v>
-      </c>
-      <c r="L28" s="36" t="s">
-        <v>287</v>
-      </c>
-      <c r="M28" s="192" t="s">
-        <v>288</v>
       </c>
       <c r="N28" s="212" t="s">
         <v>252</v>
@@ -56542,9 +57452,9 @@
         <v>251</v>
       </c>
     </row>
-    <row r="29" spans="2:18" ht="14.25" thickBot="1">
+    <row r="29" spans="2:18" ht="13.5" thickBot="1">
       <c r="B29" s="208" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C29" s="217"/>
       <c r="D29" s="217"/>
@@ -56555,13 +57465,13 @@
       <c r="I29" s="217"/>
       <c r="J29" s="217"/>
       <c r="K29" s="207" t="s">
+        <v>284</v>
+      </c>
+      <c r="L29" s="231" t="s">
+        <v>292</v>
+      </c>
+      <c r="M29" s="230" t="s">
         <v>286</v>
-      </c>
-      <c r="L29" s="231" t="s">
-        <v>294</v>
-      </c>
-      <c r="M29" s="230" t="s">
-        <v>288</v>
       </c>
       <c r="N29" s="219" t="s">
         <v>240</v>
@@ -57503,14 +58413,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="14.25" thickBot="1">
+    <row r="2" spans="2:4" ht="13.5" thickBot="1">
       <c r="B2" s="82" t="s">
         <v>84</v>
       </c>
@@ -57520,7 +58430,7 @@
       </c>
       <c r="D2" s="83"/>
     </row>
-    <row r="3" spans="2:4" ht="14.25" thickBot="1">
+    <row r="3" spans="2:4" ht="13.5" thickBot="1">
       <c r="B3" s="76" t="s">
         <v>82</v>
       </c>
@@ -57531,7 +58441,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="14.25" thickTop="1">
+    <row r="4" spans="2:4" ht="13.5" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -57542,7 +58452,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="40.5">
+    <row r="5" spans="2:4" ht="39">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -57553,7 +58463,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="27">
+    <row r="6" spans="2:4" ht="26">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -57564,7 +58474,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="54">
+    <row r="7" spans="2:4" ht="52">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -57575,7 +58485,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="81">
+    <row r="8" spans="2:4" ht="78">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -57597,7 +58507,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="27">
+    <row r="10" spans="2:4" ht="26">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -57608,7 +58518,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="27">
+    <row r="11" spans="2:4" ht="26">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -57619,7 +58529,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="27">
+    <row r="12" spans="2:4" ht="26">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -57630,7 +58540,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="27">
+    <row r="13" spans="2:4" ht="26">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -57641,7 +58551,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="27">
+    <row r="14" spans="2:4" ht="26">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -57652,7 +58562,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="135">
+    <row r="15" spans="2:4" ht="130">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -57674,7 +58584,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="27">
+    <row r="17" spans="2:4" ht="26">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -57685,7 +58595,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="67.5">
+    <row r="18" spans="2:4" ht="91">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -57696,7 +58606,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="40.5">
+    <row r="19" spans="2:4" ht="39">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -57729,26 +58639,26 @@
         <v>197</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="27">
+    <row r="22" spans="2:4" ht="26">
       <c r="B22" s="2">
         <v>18</v>
       </c>
       <c r="C22" s="86" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D22" s="88" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="27">
+    <row r="23" spans="2:4" ht="26">
       <c r="B23" s="2">
         <v>19</v>
       </c>
       <c r="C23" s="86" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D23" s="88" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -57766,7 +58676,7 @@
       <c r="C26" s="86"/>
       <c r="D26" s="72"/>
     </row>
-    <row r="27" spans="2:4" ht="14.25" thickBot="1">
+    <row r="27" spans="2:4" ht="13.5" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="87"/>
       <c r="D27" s="5"/>
